--- a/Words(音读音 & 训练音).xlsx
+++ b/Words(音读音 & 训练音).xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="975">
   <si>
     <t>名称</t>
   </si>
@@ -213,6 +213,12 @@
     <t>けっか</t>
   </si>
   <si>
+    <t>振動</t>
+  </si>
+  <si>
+    <t>しんどう</t>
+  </si>
+  <si>
     <t>特色</t>
   </si>
   <si>
@@ -226,6 +232,12 @@
   </si>
   <si>
     <t>えいきょう</t>
+  </si>
+  <si>
+    <t>更新</t>
+  </si>
+  <si>
+    <t>こうしん</t>
   </si>
   <si>
     <t>程度</t>
@@ -546,6 +558,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>（</t>
     </r>
     <r>
@@ -583,6 +601,44 @@
     <t>けいとう</t>
   </si>
   <si>
+    <t>続き</t>
+  </si>
+  <si>
+    <t>つづき</t>
+  </si>
+  <si>
+    <r>
+      <t>（前后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>联</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>系，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>继续）</t>
+    </r>
+  </si>
+  <si>
     <t>効用</t>
   </si>
   <si>
@@ -601,12 +657,30 @@
     <t>つかいみち</t>
   </si>
   <si>
+    <t>消息</t>
+  </si>
+  <si>
+    <t>しょうそく</t>
+  </si>
+  <si>
     <t>通用</t>
   </si>
   <si>
     <t>つうよう</t>
   </si>
   <si>
+    <t>境地</t>
+  </si>
+  <si>
+    <t>きょうち</t>
+  </si>
+  <si>
+    <t>（天地）</t>
+  </si>
+  <si>
+    <t>新しい境地を切り開く</t>
+  </si>
+  <si>
     <t>主題</t>
   </si>
   <si>
@@ -644,6 +718,35 @@
   </si>
   <si>
     <t>（碎片）</t>
+  </si>
+  <si>
+    <t>境</t>
+  </si>
+  <si>
+    <t>さかい</t>
+  </si>
+  <si>
+    <r>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>边</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>界）</t>
+    </r>
   </si>
   <si>
     <t>音读</t>
@@ -2514,6 +2617,12 @@
     <t>（刺し身）</t>
   </si>
   <si>
+    <t>朝ご飯</t>
+  </si>
+  <si>
+    <t>あさごはん</t>
+  </si>
+  <si>
     <t>濾過</t>
   </si>
   <si>
@@ -2543,6 +2652,12 @@
     </r>
   </si>
   <si>
+    <t>夕飯</t>
+  </si>
+  <si>
+    <t>ゆうはん</t>
+  </si>
+  <si>
     <t>舐める</t>
   </si>
   <si>
@@ -2556,6 +2671,12 @@
   </si>
   <si>
     <t>（红芋）</t>
+  </si>
+  <si>
+    <t>晩御飯</t>
+  </si>
+  <si>
+    <t>ばんごはん</t>
   </si>
   <si>
     <t>鰻</t>
@@ -2935,16 +3056,31 @@
     <t>ねんがじょう</t>
   </si>
   <si>
+    <t>倹約</t>
+  </si>
+  <si>
+    <t>けんやく</t>
+  </si>
+  <si>
+    <t>宅急便</t>
+  </si>
+  <si>
+    <t>たっきゅびん</t>
+  </si>
+  <si>
     <t>備蓄</t>
   </si>
   <si>
     <t>びちく</t>
   </si>
   <si>
-    <t>宅急便</t>
-  </si>
-  <si>
-    <t>たっきゅびん</t>
+    <t>皿</t>
+  </si>
+  <si>
+    <t>ざら</t>
+  </si>
+  <si>
+    <t>（烟灰缸）</t>
   </si>
   <si>
     <t>備蓄品</t>
@@ -2953,19 +3089,19 @@
     <t>びちくひん</t>
   </si>
   <si>
-    <t>皿</t>
-  </si>
-  <si>
-    <t>ざら</t>
-  </si>
-  <si>
-    <t>（烟灰缸）</t>
-  </si>
-  <si>
     <t>灰皿</t>
   </si>
   <si>
     <t>はいざら</t>
+  </si>
+  <si>
+    <t>お決まり</t>
+  </si>
+  <si>
+    <t>おきまり</t>
+  </si>
+  <si>
+    <t>（惯例，老习惯）</t>
   </si>
   <si>
     <t>通帳</t>
@@ -3019,6 +3155,21 @@
     </r>
   </si>
   <si>
+    <t>燃費</t>
+  </si>
+  <si>
+    <t>ねんぴ</t>
+  </si>
+  <si>
+    <t>（耗油量）</t>
+  </si>
+  <si>
+    <t>手本</t>
+  </si>
+  <si>
+    <t>てほん</t>
+  </si>
+  <si>
     <t>芸</t>
   </si>
   <si>
@@ -3456,6 +3607,12 @@
     <t>こうげいひん</t>
   </si>
   <si>
+    <t>童話</t>
+  </si>
+  <si>
+    <t>どうわ</t>
+  </si>
+  <si>
     <t>JIPT汉字整理</t>
   </si>
   <si>
@@ -3472,7 +3629,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="54">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3654,12 +3811,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF3A3A3A"/>
       <name val="Noto Sans JP"/>
@@ -3682,13 +3833,6 @@
       <color theme="1"/>
       <name val="Noto Sans JP"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -3833,16 +3977,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF3A3A3A"/>
+      <name val="Segoe UI Symbol"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF3A3A3A"/>
-      <name val="Segoe UI Symbol"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -4148,150 +4292,150 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4338,15 +4482,14 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4674,7 +4817,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:N29"/>
+  <dimension ref="A2:N30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="2"/>
@@ -4818,159 +4961,169 @@
       <c r="J6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M6" s="42"/>
+      <c r="M6" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M7" s="42"/>
+        <v>46</v>
+      </c>
+      <c r="M7" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>14</v>
@@ -4978,220 +5131,258 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -5219,28 +5410,28 @@
     <row r="1" s="13" customFormat="1" ht="18" spans="1:7">
       <c r="A1" s="15"/>
       <c r="B1" s="15" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="G1" s="15"/>
     </row>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="16" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="E2" s="16"/>
       <c r="F2" s="16"/>
@@ -5248,48 +5439,48 @@
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="16" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
     </row>
     <row r="4" ht="19.8" spans="1:7">
       <c r="A4" s="17" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
     </row>
     <row r="5" ht="36" spans="1:7">
       <c r="A5" s="16" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
@@ -5297,32 +5488,32 @@
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="16" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
     </row>
     <row r="7" ht="36" spans="1:7">
       <c r="A7" s="16" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -5331,13 +5522,13 @@
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="16" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
@@ -5346,32 +5537,32 @@
     </row>
     <row r="9" ht="19.8" spans="1:7">
       <c r="A9" s="17" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="17" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" ht="19.8" spans="1:7">
       <c r="A10" s="17" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="16"/>
@@ -5380,25 +5571,25 @@
     </row>
     <row r="11" ht="19.8" spans="1:7">
       <c r="A11" s="17" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="B11" s="19"/>
       <c r="D11" s="21" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="16"/>
     </row>
     <row r="12" ht="19.8" spans="1:7">
       <c r="A12" s="17" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B12" s="19"/>
       <c r="D12" s="4" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="17"/>
@@ -5406,47 +5597,47 @@
     </row>
     <row r="13" ht="19.8" spans="1:7">
       <c r="A13" s="17" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="4" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="F13" s="17"/>
       <c r="G13" s="16"/>
     </row>
     <row r="14" ht="19.8" spans="1:7">
       <c r="A14" s="17" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="20"/>
       <c r="D14" s="24" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="16"/>
     </row>
     <row r="15" ht="19.8" spans="1:7">
       <c r="A15" s="17" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="20"/>
       <c r="D15" s="4" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="16"/>
@@ -5462,132 +5653,132 @@
     </row>
     <row r="17" ht="19.8" spans="1:7">
       <c r="A17" s="17" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="16"/>
     </row>
     <row r="18" ht="43.2" spans="1:7">
       <c r="A18" s="17" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="20"/>
       <c r="D18" s="24" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="16"/>
     </row>
     <row r="19" ht="19.8" spans="1:7">
       <c r="A19" s="17" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="16"/>
     </row>
     <row r="20" ht="19.8" spans="1:7">
       <c r="A20" s="17" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="16"/>
     </row>
     <row r="21" ht="19.8" spans="1:7">
       <c r="A21" s="17" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="16"/>
     </row>
     <row r="22" ht="24" spans="1:7">
       <c r="A22" s="16" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:7">
       <c r="A23" s="16" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
     </row>
     <row r="24" ht="18" spans="1:7">
       <c r="A24" s="16" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
     </row>
     <row r="25" ht="18" spans="1:7">
       <c r="A25" s="16" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
@@ -5595,32 +5786,32 @@
     </row>
     <row r="26" ht="72" spans="1:7">
       <c r="A26" s="16" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
     </row>
     <row r="27" ht="18" spans="1:7">
       <c r="A27" s="16" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
@@ -5629,13 +5820,13 @@
     </row>
     <row r="28" ht="18" spans="1:7">
       <c r="A28" s="16" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
@@ -5644,26 +5835,26 @@
     </row>
     <row r="29" ht="18" spans="1:7">
       <c r="A29" s="16" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="E29" s="16"/>
       <c r="F29" s="25" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="G29" s="16"/>
     </row>
     <row r="30" ht="18" spans="1:7">
       <c r="A30" s="29" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -5674,76 +5865,76 @@
     </row>
     <row r="31" ht="18" spans="1:7">
       <c r="A31" s="16" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="25" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:7">
       <c r="A32" s="30" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="16"/>
       <c r="D32" s="25" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="F32" s="25"/>
       <c r="G32" s="25"/>
     </row>
     <row r="33" ht="18" spans="1:7">
       <c r="A33" s="31" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C33" s="16"/>
       <c r="D33" s="25" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="F33" s="25"/>
       <c r="G33" s="25"/>
     </row>
     <row r="34" ht="18" spans="1:7">
       <c r="A34" s="16" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="B34" s="16"/>
       <c r="D34" s="4" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="F34" s="16"/>
       <c r="G34" s="16"/>
     </row>
     <row r="35" ht="18" spans="1:7">
       <c r="A35" s="16" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
       <c r="D35" s="16" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
@@ -5751,7 +5942,7 @@
     </row>
     <row r="36" ht="18" spans="1:7">
       <c r="A36" s="16" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -5762,12 +5953,12 @@
     </row>
     <row r="37" ht="18" spans="1:7">
       <c r="A37" s="32" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
       <c r="D37" s="33" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="E37" s="16"/>
       <c r="F37" s="16"/>
@@ -5775,45 +5966,45 @@
     </row>
     <row r="38" ht="18" spans="1:7">
       <c r="A38" s="16" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
       <c r="D38" s="7" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="E38" s="16"/>
       <c r="F38" s="4" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="G38" s="16"/>
     </row>
     <row r="39" ht="18" spans="1:7">
       <c r="A39" s="16" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
       <c r="D39" s="4" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="G39" s="16"/>
     </row>
     <row r="40" ht="18" spans="1:7">
       <c r="A40" s="16" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="16"/>
@@ -5822,10 +6013,10 @@
     </row>
     <row r="41" ht="18" spans="1:7">
       <c r="A41" s="16" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
@@ -5835,10 +6026,10 @@
     </row>
     <row r="42" ht="18" spans="1:7">
       <c r="A42" s="16" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
@@ -5848,7 +6039,7 @@
     </row>
     <row r="43" ht="18" spans="1:7">
       <c r="A43" s="16" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="B43" s="16"/>
       <c r="D43" s="16"/>
@@ -5858,7 +6049,7 @@
     </row>
     <row r="44" ht="18" spans="1:7">
       <c r="A44" s="16" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B44" s="16"/>
       <c r="D44" s="16"/>
@@ -5868,83 +6059,83 @@
     </row>
     <row r="45" ht="18" spans="1:7">
       <c r="A45" s="16" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="F45" s="16"/>
       <c r="G45" s="16"/>
     </row>
     <row r="46" ht="43.2" spans="1:7">
       <c r="A46" s="16" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="F46" s="16"/>
       <c r="G46" s="16"/>
     </row>
     <row r="47" ht="28.8" spans="1:7">
       <c r="A47" s="16" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
       <c r="D47" s="4" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="G47" s="25" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:7">
       <c r="A48" s="16" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
       <c r="D48" s="4"/>
       <c r="E48" s="25" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="25"/>
     </row>
     <row r="49" ht="36" spans="1:7">
       <c r="A49" s="16" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="25"/>
@@ -5953,13 +6144,13 @@
     </row>
     <row r="50" ht="36" spans="1:7">
       <c r="A50" s="7" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="16"/>
@@ -5968,7 +6159,7 @@
     </row>
     <row r="51" ht="18" spans="1:7">
       <c r="A51" s="16" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -5979,7 +6170,7 @@
     </row>
     <row r="52" ht="18" spans="1:7">
       <c r="A52" s="16" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -5990,7 +6181,7 @@
     </row>
     <row r="53" ht="18" spans="1:7">
       <c r="A53" s="16" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -6001,24 +6192,24 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="14" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:7">
       <c r="A55" s="16" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="16"/>
@@ -6027,13 +6218,13 @@
     </row>
     <row r="56" ht="18" spans="1:7">
       <c r="A56" s="3" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="16"/>
@@ -6042,54 +6233,54 @@
     </row>
     <row r="57" ht="36" spans="1:7">
       <c r="A57" s="16" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="F57" s="34" t="s">
-        <v>249</v>
+        <v>332</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>265</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:7">
       <c r="A58" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="B58" s="35" t="s">
-        <v>220</v>
+        <v>334</v>
+      </c>
+      <c r="B58" s="34" t="s">
+        <v>236</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="D58" s="33" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="F58" s="16"/>
       <c r="G58" s="16"/>
     </row>
     <row r="59" ht="18" spans="1:7">
       <c r="A59" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="B59" s="35"/>
+        <v>338</v>
+      </c>
+      <c r="B59" s="34"/>
       <c r="C59" s="16"/>
       <c r="D59" s="16" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
@@ -6097,12 +6288,12 @@
     </row>
     <row r="60" ht="18" spans="1:7">
       <c r="A60" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="B60" s="35"/>
+        <v>340</v>
+      </c>
+      <c r="B60" s="34"/>
       <c r="C60" s="16"/>
       <c r="D60" s="16" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
@@ -6110,56 +6301,56 @@
     </row>
     <row r="61" ht="18" spans="1:7">
       <c r="A61" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="B61" s="35"/>
+        <v>342</v>
+      </c>
+      <c r="B61" s="34"/>
       <c r="C61" s="16"/>
       <c r="D61" s="16" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="F61" s="16"/>
       <c r="G61" s="16"/>
     </row>
     <row r="62" ht="18" spans="1:7">
       <c r="A62" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B62" s="35"/>
+        <v>345</v>
+      </c>
+      <c r="B62" s="34"/>
       <c r="C62" s="16"/>
       <c r="D62" s="16" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="F62" s="16"/>
       <c r="G62" s="16"/>
     </row>
     <row r="63" ht="18" hidden="1" spans="1:7">
       <c r="A63" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="B63" s="35"/>
+        <v>348</v>
+      </c>
+      <c r="B63" s="34"/>
       <c r="C63" s="16"/>
       <c r="D63" s="16" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="16"/>
     </row>
     <row r="64" ht="36" spans="1:7">
-      <c r="A64" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="B64" s="36" t="s">
-        <v>335</v>
+      <c r="A64" s="35" t="s">
+        <v>350</v>
+      </c>
+      <c r="B64" s="35" t="s">
+        <v>351</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
@@ -6168,13 +6359,13 @@
     </row>
     <row r="65" ht="18" spans="1:7">
       <c r="A65" s="16" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
@@ -6183,13 +6374,13 @@
     </row>
     <row r="66" ht="18" spans="1:7">
       <c r="A66" s="16" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="16"/>
@@ -6198,13 +6389,13 @@
     </row>
     <row r="67" ht="36" spans="1:7">
       <c r="A67" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="B67" s="35" t="s">
-        <v>344</v>
+        <v>359</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>360</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="D67" s="16"/>
       <c r="E67" s="16"/>
@@ -6213,16 +6404,16 @@
     </row>
     <row r="68" ht="18" spans="1:7">
       <c r="A68" s="16" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="B68" s="32" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="C68" s="32" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="E68" s="16"/>
       <c r="F68" s="16"/>
@@ -6230,12 +6421,12 @@
     </row>
     <row r="69" ht="18" spans="1:7">
       <c r="A69" s="16" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
       <c r="D69" s="16" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="E69" s="16"/>
       <c r="F69" s="16"/>
@@ -6243,16 +6434,16 @@
     </row>
     <row r="70" ht="19.8" spans="1:7">
       <c r="A70" s="16" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="E70" s="16"/>
       <c r="F70" s="16"/>
@@ -6260,33 +6451,33 @@
     </row>
     <row r="71" ht="36" spans="1:7">
       <c r="A71" s="16" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="F71" s="16"/>
       <c r="G71" s="16"/>
     </row>
     <row r="72" ht="19.8" spans="1:7">
       <c r="A72" s="16" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C72" s="16"/>
       <c r="D72" s="17" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="E72" s="17"/>
       <c r="F72" s="16"/>
@@ -6294,10 +6485,10 @@
     </row>
     <row r="73" ht="19.8" spans="1:7">
       <c r="A73" s="16" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C73" s="16"/>
       <c r="D73" s="17"/>
@@ -6307,50 +6498,50 @@
     </row>
     <row r="74" ht="19.8" spans="1:7">
       <c r="A74" s="16" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C74" s="16"/>
-      <c r="D74" s="35" t="s">
-        <v>249</v>
+      <c r="D74" s="34" t="s">
+        <v>265</v>
       </c>
       <c r="E74" s="17"/>
       <c r="F74" s="24" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
     </row>
     <row r="75" ht="19.8" spans="1:7">
       <c r="A75" s="16" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="D75" s="35" t="s">
-        <v>367</v>
+        <v>382</v>
+      </c>
+      <c r="D75" s="34" t="s">
+        <v>383</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="G75" s="16"/>
     </row>
     <row r="76" ht="19.8" spans="1:7">
       <c r="A76" s="16" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C76" s="16"/>
       <c r="D76" s="17"/>
@@ -6360,10 +6551,10 @@
     </row>
     <row r="77" ht="19.8" spans="1:7">
       <c r="A77" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="B77" s="17" t="s">
         <v>371</v>
-      </c>
-      <c r="B77" s="17" t="s">
-        <v>355</v>
       </c>
       <c r="C77" s="16"/>
       <c r="D77" s="17"/>
@@ -6373,13 +6564,13 @@
     </row>
     <row r="78" ht="36" spans="1:7">
       <c r="A78" s="16" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="D78" s="17"/>
       <c r="E78" s="17"/>
@@ -6388,32 +6579,32 @@
     </row>
     <row r="79" ht="18" spans="1:7">
       <c r="A79" s="16" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="F79" s="16"/>
       <c r="G79" s="16"/>
     </row>
     <row r="80" ht="19.8" spans="1:7">
       <c r="A80" s="17" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="D80" s="16"/>
       <c r="E80" s="16"/>
@@ -6422,13 +6613,13 @@
     </row>
     <row r="81" ht="19.8" spans="1:7">
       <c r="A81" s="17" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="D81" s="16"/>
       <c r="E81" s="16"/>
@@ -6437,13 +6628,13 @@
     </row>
     <row r="82" ht="18" spans="1:7">
       <c r="A82" s="16" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="D82" s="16"/>
       <c r="E82" s="16"/>
@@ -6452,44 +6643,44 @@
     </row>
     <row r="83" ht="36" spans="1:7">
       <c r="A83" s="32" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
       <c r="D83" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="E83" s="37" t="s">
-        <v>386</v>
+        <v>277</v>
+      </c>
+      <c r="E83" s="36" t="s">
+        <v>402</v>
       </c>
       <c r="F83" s="16"/>
       <c r="G83" s="16"/>
     </row>
     <row r="84" ht="18" spans="1:7">
       <c r="A84" s="32" t="s">
-        <v>387</v>
-      </c>
-      <c r="D84" s="35" t="s">
-        <v>388</v>
+        <v>403</v>
+      </c>
+      <c r="D84" s="34" t="s">
+        <v>404</v>
       </c>
       <c r="E84" s="32" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="F84" s="16"/>
       <c r="G84" s="16"/>
     </row>
     <row r="85" ht="18" spans="1:7">
       <c r="A85" s="32" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="C85" s="32" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="D85" s="24" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="E85" s="16"/>
       <c r="F85" s="16"/>
@@ -6497,56 +6688,56 @@
     </row>
     <row r="86" ht="18" spans="1:7">
       <c r="A86" s="16" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="B86" s="16"/>
       <c r="D86" s="16" t="s">
-        <v>395</v>
-      </c>
-      <c r="E86" s="38" t="s">
-        <v>396</v>
+        <v>411</v>
+      </c>
+      <c r="E86" s="37" t="s">
+        <v>412</v>
       </c>
       <c r="F86" s="16"/>
       <c r="G86" s="16"/>
     </row>
     <row r="87" ht="18" spans="1:7">
       <c r="A87" s="16" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="B87" s="16"/>
       <c r="C87" s="16"/>
       <c r="D87" s="16" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="F87" s="16"/>
       <c r="G87" s="16"/>
     </row>
     <row r="88" ht="18" spans="1:7">
       <c r="A88" s="16" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
       <c r="D88" s="16" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="F88" s="16"/>
       <c r="G88" s="16"/>
     </row>
     <row r="89" ht="18" spans="1:7">
       <c r="A89" s="16" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B89" s="16"/>
       <c r="C89" s="16"/>
-      <c r="D89" s="39" t="s">
-        <v>404</v>
+      <c r="D89" s="38" t="s">
+        <v>420</v>
       </c>
       <c r="E89" s="16"/>
       <c r="F89" s="16"/>
@@ -6554,42 +6745,42 @@
     </row>
     <row r="90" ht="36" spans="1:7">
       <c r="A90" s="16" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="C90" s="18" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
     </row>
     <row r="91" ht="18" spans="1:7">
       <c r="A91" s="16" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="B91" s="16"/>
       <c r="C91" s="16"/>
       <c r="D91" s="16" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="E91" s="16"/>
       <c r="F91" s="4" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
     </row>
     <row r="92" ht="18" spans="1:7">
       <c r="A92" s="16" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="B92" s="16"/>
       <c r="C92" s="16"/>
       <c r="D92" s="16" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="E92" s="16"/>
       <c r="F92" s="16"/>
@@ -6597,60 +6788,60 @@
     </row>
     <row r="93" ht="18" spans="1:7">
       <c r="A93" s="16" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="B93" s="16"/>
       <c r="C93" s="16"/>
       <c r="D93" s="16" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="F93" s="16"/>
       <c r="G93" s="16"/>
     </row>
     <row r="94" ht="18" spans="1:7">
       <c r="A94" s="16" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="B94" s="16"/>
       <c r="C94" s="16"/>
-      <c r="D94" s="40" t="s">
-        <v>416</v>
+      <c r="D94" s="39" t="s">
+        <v>432</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="F94" s="16"/>
       <c r="G94" s="16"/>
     </row>
     <row r="95" ht="19.8" spans="1:7">
       <c r="A95" s="16" t="s">
-        <v>418</v>
-      </c>
-      <c r="B95" s="41" t="s">
-        <v>419</v>
+        <v>434</v>
+      </c>
+      <c r="B95" s="40" t="s">
+        <v>435</v>
       </c>
       <c r="C95" s="16"/>
       <c r="D95" s="16" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F95" s="16"/>
       <c r="G95" s="16"/>
     </row>
     <row r="96" ht="36" spans="1:7">
       <c r="A96" s="16" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="D96" s="16"/>
       <c r="E96" s="16"/>
@@ -6659,12 +6850,12 @@
     </row>
     <row r="97" ht="18" spans="1:7">
       <c r="A97" s="19" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="B97" s="16"/>
       <c r="C97" s="16"/>
       <c r="D97" s="19" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="E97" s="16"/>
       <c r="F97" s="16"/>
@@ -6672,20 +6863,20 @@
     </row>
     <row r="98" ht="18" spans="1:7">
       <c r="A98" s="16" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="C98" s="16"/>
-      <c r="D98" s="35" t="s">
-        <v>428</v>
+      <c r="D98" s="34" t="s">
+        <v>444</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="G98" s="16"/>
     </row>
@@ -6709,309 +6900,309 @@
   <sheetData>
     <row r="1" ht="18" spans="1:13">
       <c r="I1" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="L1" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:13">
       <c r="A2" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="K2" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="B3" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="E3" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="G3" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="K3" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="G4" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="E5" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:13">
       <c r="E6" s="2" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:13">
       <c r="A7" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:13">
       <c r="A8" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="E8" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:13">
       <c r="A9" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="C10" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="C11" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="I11" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="C14" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="K14" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" ht="18" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="C16" s="12"/>
       <c r="I16" s="2"/>
@@ -7019,10 +7210,10 @@
     </row>
     <row r="17" ht="18" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="C17" s="12"/>
       <c r="I17" s="2"/>
@@ -7034,68 +7225,68 @@
     </row>
     <row r="19" ht="18" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:10">
       <c r="A20" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>537</v>
+        <v>553</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>539</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -7120,661 +7311,677 @@
   <sheetData>
     <row r="1" ht="18" spans="1:20">
       <c r="A1" s="2" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:20">
       <c r="A2" s="8" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="G2" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="I2" t="s">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>551</v>
+        <v>567</v>
       </c>
       <c r="O2" t="s">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:20">
       <c r="A3" s="8" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="G3" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>563</v>
+        <v>579</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:20">
       <c r="A4" s="2" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="G4" t="s">
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="K4" t="s">
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="L4" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="M4" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="O4" t="s">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="P4" t="s">
-        <v>574</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:20">
       <c r="A5" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>576</v>
+        <v>592</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>579</v>
+        <v>595</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>583</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:20">
       <c r="A6" s="8" t="s">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="G6" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:20">
       <c r="A7" s="8" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="Q7" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:20">
       <c r="A8" s="8" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="G8" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="K8" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="L8" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:20">
       <c r="A9" s="8" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>618</v>
+        <v>634</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>619</v>
+        <v>635</v>
       </c>
       <c r="G9" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>624</v>
+        <v>640</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>625</v>
+        <v>641</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>626</v>
+        <v>642</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:20">
       <c r="A10" s="2" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="B10" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
       <c r="I10" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>635</v>
+        <v>651</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>636</v>
+        <v>652</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>637</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:20">
       <c r="A11" s="2" t="s">
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
       <c r="I11" t="s">
-        <v>642</v>
+        <v>658</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>644</v>
+        <v>660</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
       <c r="Q11" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:20">
       <c r="A12" s="8" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="I12" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:20">
       <c r="A13" s="2" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>656</v>
+        <v>672</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>658</v>
+        <v>674</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
       <c r="Q13" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:20">
       <c r="A14" s="2" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="Q14" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:20">
       <c r="A15" t="s">
-        <v>668</v>
+        <v>684</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>671</v>
+        <v>687</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>672</v>
+        <v>688</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:20">
       <c r="A16" s="10" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="O16" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="A17" s="10" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" s="10" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>687</v>
+        <v>703</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+        <v>704</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>706</v>
+      </c>
       <c r="O18" s="2" t="s">
-        <v>689</v>
+        <v>707</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>690</v>
+        <v>708</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="A19" s="2" t="s">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>692</v>
+        <v>710</v>
+      </c>
+      <c r="G19" t="s">
+        <v>711</v>
+      </c>
+      <c r="H19" t="s">
+        <v>712</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="A20" s="2" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="C20" t="s">
-        <v>697</v>
+        <v>717</v>
+      </c>
+      <c r="G20" t="s">
+        <v>718</v>
+      </c>
+      <c r="H20" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
       <c r="A21" s="2" t="s">
-        <v>698</v>
+        <v>720</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>699</v>
+        <v>721</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2" t="s">
-        <v>700</v>
+        <v>722</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>701</v>
+        <v>723</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2" t="s">
-        <v>702</v>
+        <v>724</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>703</v>
+        <v>725</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>704</v>
+        <v>726</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>705</v>
+        <v>727</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" t="s">
-        <v>706</v>
+        <v>728</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>707</v>
+        <v>729</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="A26" s="2" t="s">
-        <v>708</v>
+        <v>730</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>709</v>
+        <v>731</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="A27" s="11" t="s">
-        <v>710</v>
+        <v>732</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>711</v>
+        <v>733</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="A28" s="2" t="s">
-        <v>712</v>
+        <v>734</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>713</v>
+        <v>735</v>
       </c>
       <c r="C28" t="s">
-        <v>714</v>
+        <v>736</v>
       </c>
       <c r="E28" t="s">
-        <v>715</v>
+        <v>737</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="A29" s="2" t="s">
-        <v>716</v>
+        <v>738</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>715</v>
+        <v>737</v>
       </c>
       <c r="C29" t="s">
-        <v>717</v>
+        <v>739</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="A30" t="s">
-        <v>718</v>
+        <v>740</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>719</v>
+        <v>741</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
       <c r="A31" s="2" t="s">
-        <v>720</v>
+        <v>742</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>721</v>
+        <v>743</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>722</v>
+        <v>744</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>723</v>
+        <v>745</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:2">
       <c r="A33" s="2" t="s">
-        <v>724</v>
+        <v>746</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>725</v>
+        <v>747</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>726</v>
+        <v>748</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>727</v>
+        <v>749</v>
       </c>
     </row>
   </sheetData>
@@ -7786,7 +7993,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G20"/>
+  <dimension ref="A2:G22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -7796,256 +8003,290 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>728</v>
+        <v>750</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" t="s">
-        <v>729</v>
+        <v>751</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>730</v>
+        <v>752</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>731</v>
+        <v>753</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>732</v>
+        <v>754</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>733</v>
+        <v>755</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>734</v>
+        <v>756</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>735</v>
+        <v>757</v>
       </c>
       <c r="D4" t="s">
-        <v>736</v>
+        <v>758</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>737</v>
+        <v>759</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>738</v>
+        <v>760</v>
       </c>
       <c r="D5" t="s">
-        <v>739</v>
+        <v>761</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>740</v>
+        <v>762</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>741</v>
+        <v>763</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>742</v>
+        <v>764</v>
       </c>
       <c r="D6" t="s">
-        <v>743</v>
+        <v>765</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>744</v>
+        <v>766</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>745</v>
+        <v>767</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>746</v>
+        <v>768</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>747</v>
+        <v>769</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>749</v>
+        <v>771</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>750</v>
+        <v>772</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>751</v>
+        <v>773</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>753</v>
+        <v>775</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>754</v>
+        <v>776</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>755</v>
+        <v>777</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>756</v>
+        <v>778</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>757</v>
+        <v>779</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>758</v>
+        <v>780</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>759</v>
+        <v>781</v>
       </c>
       <c r="C9" t="s">
-        <v>760</v>
+        <v>782</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>761</v>
+        <v>783</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>762</v>
+        <v>784</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>763</v>
+        <v>785</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>764</v>
+        <v>786</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>765</v>
+        <v>787</v>
       </c>
       <c r="C10" t="s">
-        <v>766</v>
+        <v>788</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>767</v>
+        <v>789</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>768</v>
+        <v>790</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>770</v>
+        <v>792</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>771</v>
+        <v>793</v>
       </c>
       <c r="C11" t="s">
-        <v>772</v>
+        <v>794</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>773</v>
+        <v>795</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>774</v>
+        <v>796</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>775</v>
+        <v>797</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>778</v>
+        <v>798</v>
+      </c>
+      <c r="D12" t="s">
+        <v>799</v>
+      </c>
+      <c r="E12" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>779</v>
+        <v>801</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>780</v>
+        <v>802</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>781</v>
+        <v>803</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>782</v>
+        <v>804</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>783</v>
+        <v>805</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>784</v>
+        <v>806</v>
       </c>
       <c r="C14" t="s">
-        <v>785</v>
+        <v>807</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>786</v>
+        <v>810</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>787</v>
+        <v>811</v>
+      </c>
+      <c r="D15" t="s">
+        <v>812</v>
+      </c>
+      <c r="E15" t="s">
+        <v>813</v>
+      </c>
+      <c r="F15" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:7">
       <c r="A16" s="7" t="s">
-        <v>788</v>
+        <v>815</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>789</v>
+        <v>816</v>
       </c>
     </row>
     <row r="17" ht="15.6" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>790</v>
+        <v>817</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>791</v>
+        <v>818</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>792</v>
+        <v>819</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>793</v>
+        <v>820</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>794</v>
+        <v>821</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>795</v>
+        <v>822</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>796</v>
+        <v>823</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>798</v>
+        <v>825</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>826</v>
+      </c>
+      <c r="B21" t="s">
+        <v>827</v>
+      </c>
+      <c r="C21" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>829</v>
+      </c>
+      <c r="B22" t="s">
+        <v>830</v>
       </c>
     </row>
   </sheetData>
@@ -8068,306 +8309,306 @@
   <sheetData>
     <row r="2" ht="18" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>799</v>
+        <v>831</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>800</v>
+        <v>832</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>802</v>
+        <v>834</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>803</v>
+        <v>835</v>
       </c>
       <c r="K2" t="s">
-        <v>804</v>
+        <v>836</v>
       </c>
       <c r="L2" t="s">
-        <v>805</v>
+        <v>837</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>806</v>
+        <v>838</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>807</v>
+        <v>839</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>808</v>
+        <v>840</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>809</v>
+        <v>841</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>810</v>
+        <v>842</v>
       </c>
       <c r="K3" t="s">
-        <v>811</v>
+        <v>843</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>812</v>
+        <v>844</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>813</v>
+        <v>845</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>814</v>
+        <v>846</v>
       </c>
       <c r="C4" t="s">
-        <v>815</v>
+        <v>847</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>816</v>
+        <v>848</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>817</v>
+        <v>849</v>
       </c>
       <c r="H4" t="s">
-        <v>818</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>819</v>
+        <v>851</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>820</v>
+        <v>852</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>821</v>
+        <v>853</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>822</v>
+        <v>854</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>823</v>
+        <v>855</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>824</v>
+        <v>856</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>825</v>
+        <v>857</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>826</v>
+        <v>858</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>827</v>
+        <v>859</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>828</v>
+        <v>860</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>829</v>
+        <v>861</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" ht="18" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>830</v>
+        <v>862</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>831</v>
+        <v>863</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>832</v>
+        <v>864</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>833</v>
+        <v>865</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>834</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>836</v>
+        <v>868</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>837</v>
+        <v>869</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>838</v>
+        <v>870</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>839</v>
+        <v>871</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>840</v>
+        <v>872</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>841</v>
+        <v>873</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>842</v>
+        <v>874</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>843</v>
+        <v>875</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>844</v>
+        <v>876</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>845</v>
+        <v>877</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>846</v>
+        <v>878</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>847</v>
+        <v>879</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>848</v>
+        <v>880</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>849</v>
+        <v>881</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>850</v>
+        <v>882</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>851</v>
+        <v>883</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>852</v>
+        <v>884</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>853</v>
+        <v>885</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>854</v>
+        <v>886</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>855</v>
+        <v>887</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>855</v>
+        <v>887</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>856</v>
+        <v>888</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>857</v>
+        <v>889</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>858</v>
+        <v>890</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>859</v>
+        <v>891</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>860</v>
+        <v>892</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>861</v>
+        <v>893</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>862</v>
+        <v>894</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>863</v>
+        <v>895</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>864</v>
+        <v>896</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>865</v>
+        <v>897</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>866</v>
+        <v>898</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>867</v>
+        <v>899</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>869</v>
+        <v>901</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>870</v>
+        <v>902</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>871</v>
+        <v>903</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>873</v>
+        <v>905</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>875</v>
+        <v>907</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>876</v>
+        <v>908</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>877</v>
+        <v>909</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>878</v>
+        <v>910</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>879</v>
+        <v>911</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>880</v>
+        <v>912</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>881</v>
+        <v>913</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="G18" t="s">
-        <v>883</v>
+        <v>915</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>884</v>
+        <v>916</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>885</v>
+        <v>917</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -8389,7 +8630,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9.55555555555556" style="2" customWidth="1"/>
@@ -8407,229 +8648,237 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>887</v>
+        <v>919</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>888</v>
+        <v>920</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>889</v>
+        <v>921</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>890</v>
+        <v>922</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>891</v>
+        <v>923</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>876</v>
+        <v>908</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>877</v>
+        <v>909</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>892</v>
+        <v>924</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>893</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>894</v>
+        <v>926</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>895</v>
+        <v>927</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>896</v>
+        <v>928</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>897</v>
+        <v>929</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>898</v>
+        <v>930</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>899</v>
+        <v>931</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>901</v>
+        <v>933</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>902</v>
+        <v>934</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>903</v>
+        <v>935</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>904</v>
+        <v>936</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>905</v>
+        <v>937</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>906</v>
+        <v>938</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>907</v>
+        <v>939</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>908</v>
+        <v>940</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>909</v>
+        <v>941</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>910</v>
+        <v>942</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>911</v>
+        <v>943</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>912</v>
+        <v>944</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>914</v>
+        <v>946</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>915</v>
+        <v>947</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>916</v>
+        <v>948</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>917</v>
+        <v>949</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>918</v>
+        <v>950</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>919</v>
+        <v>951</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>920</v>
+        <v>952</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>921</v>
+        <v>953</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>922</v>
+        <v>954</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>923</v>
+        <v>955</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>924</v>
+        <v>956</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>927</v>
+        <v>959</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>929</v>
+        <v>961</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>930</v>
+        <v>962</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>931</v>
+        <v>963</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>932</v>
+        <v>964</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>870</v>
+        <v>902</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>871</v>
+        <v>903</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>933</v>
+        <v>965</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>934</v>
+        <v>966</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>935</v>
+        <v>967</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>936</v>
+        <v>968</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>937</v>
+        <v>969</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>938</v>
+        <v>970</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>972</v>
       </c>
     </row>
   </sheetData>
@@ -8649,10 +8898,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>939</v>
+        <v>973</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>940</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>

--- a/Words(音读音 & 训练音).xlsx
+++ b/Words(音读音 & 训练音).xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="981">
   <si>
     <t>名称</t>
   </si>
@@ -88,12 +88,6 @@
     <t>いんが</t>
   </si>
   <si>
-    <t>代用</t>
-  </si>
-  <si>
-    <t>だいよう</t>
-  </si>
-  <si>
     <t>規格</t>
   </si>
   <si>
@@ -112,12 +106,6 @@
     <t>かてい</t>
   </si>
   <si>
-    <t>緩和</t>
-  </si>
-  <si>
-    <t>かんわ</t>
-  </si>
-  <si>
     <t>品質</t>
   </si>
   <si>
@@ -134,12 +122,6 @@
   </si>
   <si>
     <t>よき</t>
-  </si>
-  <si>
-    <t>爆発</t>
-  </si>
-  <si>
-    <t>ばくはつ</t>
   </si>
   <si>
     <t>勢い</t>
@@ -189,12 +171,6 @@
     <t>げんいん</t>
   </si>
   <si>
-    <t>旺盛</t>
-  </si>
-  <si>
-    <t>おうせい</t>
-  </si>
-  <si>
     <t>特徴</t>
   </si>
   <si>
@@ -213,12 +189,6 @@
     <t>けっか</t>
   </si>
   <si>
-    <t>振動</t>
-  </si>
-  <si>
-    <t>しんどう</t>
-  </si>
-  <si>
     <t>特色</t>
   </si>
   <si>
@@ -232,12 +202,6 @@
   </si>
   <si>
     <t>えいきょう</t>
-  </si>
-  <si>
-    <t>更新</t>
-  </si>
-  <si>
-    <t>こうしん</t>
   </si>
   <si>
     <t>程度</t>
@@ -497,49 +461,52 @@
     <t>しゅんかん</t>
   </si>
   <si>
+    <t>屑</t>
+  </si>
+  <si>
+    <t>くず</t>
+  </si>
+  <si>
+    <t>（碎片）</t>
+  </si>
+  <si>
+    <t>現実</t>
+  </si>
+  <si>
+    <t>げんじつ</t>
+  </si>
+  <si>
+    <t>選択</t>
+  </si>
+  <si>
+    <t>せんたく</t>
+  </si>
+  <si>
+    <t>芯</t>
+  </si>
+  <si>
+    <t>しん</t>
+  </si>
+  <si>
+    <t>手際</t>
+  </si>
+  <si>
+    <t>てぎわ</t>
+  </si>
+  <si>
+    <t>（技巧）</t>
+  </si>
+  <si>
+    <t>相性</t>
+  </si>
+  <si>
+    <t>あいしょう</t>
+  </si>
+  <si>
     <t>要素</t>
   </si>
   <si>
     <t>ようそ</t>
-  </si>
-  <si>
-    <t>現実</t>
-  </si>
-  <si>
-    <t>げんじつ</t>
-  </si>
-  <si>
-    <t>選択</t>
-  </si>
-  <si>
-    <t>せんたく</t>
-  </si>
-  <si>
-    <t>類別</t>
-  </si>
-  <si>
-    <t>るいべつ</t>
-  </si>
-  <si>
-    <t>手際</t>
-  </si>
-  <si>
-    <t>てぎわ</t>
-  </si>
-  <si>
-    <t>（技巧）</t>
-  </si>
-  <si>
-    <t>相性</t>
-  </si>
-  <si>
-    <t>あいしょう</t>
-  </si>
-  <si>
-    <t>意義</t>
-  </si>
-  <si>
-    <t>いぎ</t>
   </si>
   <si>
     <t>知らせ</t>
@@ -589,10 +556,10 @@
     <t>アジア諸国との連帯</t>
   </si>
   <si>
-    <t>用途</t>
-  </si>
-  <si>
-    <t>ようと</t>
+    <t>類別</t>
+  </si>
+  <si>
+    <t>るいべつ</t>
   </si>
   <si>
     <t>系統</t>
@@ -608,6 +575,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>（前后</t>
     </r>
     <r>
@@ -639,16 +612,55 @@
     </r>
   </si>
   <si>
+    <t>意義</t>
+  </si>
+  <si>
+    <t>いぎ</t>
+  </si>
+  <si>
+    <t>種類</t>
+  </si>
+  <si>
+    <t>しゅるい</t>
+  </si>
+  <si>
+    <t>格差</t>
+  </si>
+  <si>
+    <t>かくさ</t>
+  </si>
+  <si>
+    <t>（差别）</t>
+  </si>
+  <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>ようと</t>
+  </si>
+  <si>
+    <t>消息</t>
+  </si>
+  <si>
+    <t>しょうそく</t>
+  </si>
+  <si>
     <t>効用</t>
   </si>
   <si>
     <t>こうよう</t>
   </si>
   <si>
-    <t>種類</t>
-  </si>
-  <si>
-    <t>しゅるい</t>
+    <t>境地</t>
+  </si>
+  <si>
+    <t>きょうち</t>
+  </si>
+  <si>
+    <t>（天地）</t>
+  </si>
+  <si>
+    <t>新しい境地を切り開く</t>
   </si>
   <si>
     <t>使い道</t>
@@ -657,30 +669,12 @@
     <t>つかいみち</t>
   </si>
   <si>
-    <t>消息</t>
-  </si>
-  <si>
-    <t>しょうそく</t>
-  </si>
-  <si>
     <t>通用</t>
   </si>
   <si>
     <t>つうよう</t>
   </si>
   <si>
-    <t>境地</t>
-  </si>
-  <si>
-    <t>きょうち</t>
-  </si>
-  <si>
-    <t>（天地）</t>
-  </si>
-  <si>
-    <t>新しい境地を切り開く</t>
-  </si>
-  <si>
     <t>主題</t>
   </si>
   <si>
@@ -711,15 +705,6 @@
     <t>きみょう</t>
   </si>
   <si>
-    <t>屑</t>
-  </si>
-  <si>
-    <t>くず</t>
-  </si>
-  <si>
-    <t>（碎片）</t>
-  </si>
-  <si>
     <t>境</t>
   </si>
   <si>
@@ -727,6 +712,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>（</t>
     </r>
     <r>
@@ -749,6 +740,32 @@
     </r>
   </si>
   <si>
+    <t>見事</t>
+  </si>
+  <si>
+    <t>みごと</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（美</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>丽）</t>
+    </r>
+  </si>
+  <si>
     <t>音读</t>
   </si>
   <si>
@@ -1419,9 +1436,6 @@
     <t>新</t>
   </si>
   <si>
-    <t>しん</t>
-  </si>
-  <si>
     <t>新聞｜しんぶん
 朝日新聞｜あさひしんぶん</t>
   </si>
@@ -1466,9 +1480,6 @@
   </si>
   <si>
     <t>震</t>
-  </si>
-  <si>
-    <t>芯</t>
   </si>
   <si>
     <t>生</t>
@@ -2679,10 +2690,22 @@
     <t>ばんごはん</t>
   </si>
   <si>
+    <t>熱する</t>
+  </si>
+  <si>
+    <t>ねっする</t>
+  </si>
+  <si>
     <t>鰻</t>
   </si>
   <si>
     <t>うなぎ</t>
+  </si>
+  <si>
+    <t>冷たくなる</t>
+  </si>
+  <si>
+    <t>つめたくなる</t>
   </si>
   <si>
     <t>鰻丼</t>
@@ -2814,22 +2837,22 @@
     <t>ほどく</t>
   </si>
   <si>
+    <t>刀</t>
+  </si>
+  <si>
+    <t>かたな</t>
+  </si>
+  <si>
+    <t>洗濯</t>
+  </si>
+  <si>
+    <t>（洗衣服）</t>
+  </si>
+  <si>
     <t>新聞</t>
   </si>
   <si>
     <t>しんぶん</t>
-  </si>
-  <si>
-    <t>洗濯</t>
-  </si>
-  <si>
-    <t>（洗衣服）</t>
-  </si>
-  <si>
-    <t>書留</t>
-  </si>
-  <si>
-    <t>かきとめ</t>
   </si>
   <si>
     <t>支度</t>
@@ -2885,13 +2908,10 @@
     </r>
   </si>
   <si>
-    <t>お電話</t>
-  </si>
-  <si>
-    <t>おでんわ</t>
-  </si>
-  <si>
-    <t>学生手帳｜がくせいてちょう</t>
+    <t>書留</t>
+  </si>
+  <si>
+    <t>かきとめ</t>
   </si>
   <si>
     <t>炊事</t>
@@ -2929,10 +2949,13 @@
     </r>
   </si>
   <si>
-    <t>手帳、手帖</t>
-  </si>
-  <si>
-    <t>てちょう</t>
+    <t>お電話</t>
+  </si>
+  <si>
+    <t>おでんわ</t>
+  </si>
+  <si>
+    <t>学生手帳｜がくせいてちょう</t>
   </si>
   <si>
     <t>ごみ</t>
@@ -2973,6 +2996,21 @@
     <t>ゴミ箱</t>
   </si>
   <si>
+    <t>手帳、手帖</t>
+  </si>
+  <si>
+    <t>てちょう</t>
+  </si>
+  <si>
+    <t>引っ越し</t>
+  </si>
+  <si>
+    <t>ひっこし</t>
+  </si>
+  <si>
+    <t>（搬家）</t>
+  </si>
+  <si>
     <t>手紙</t>
   </si>
   <si>
@@ -2980,24 +3018,6 @@
   </si>
   <si>
     <t>（话剧，戏剧）</t>
-  </si>
-  <si>
-    <t>引っ越し</t>
-  </si>
-  <si>
-    <t>ひっこし</t>
-  </si>
-  <si>
-    <t>（搬家）</t>
-  </si>
-  <si>
-    <t>芝居</t>
-  </si>
-  <si>
-    <t>しばい</t>
-  </si>
-  <si>
-    <t>（明信片）</t>
   </si>
   <si>
     <t>時間割</t>
@@ -3035,6 +3055,21 @@
     </r>
   </si>
   <si>
+    <t>芝居</t>
+  </si>
+  <si>
+    <t>しばい</t>
+  </si>
+  <si>
+    <t>（明信片）</t>
+  </si>
+  <si>
+    <t>節約</t>
+  </si>
+  <si>
+    <t>せつやく</t>
+  </si>
+  <si>
     <t>賀状</t>
   </si>
   <si>
@@ -3044,10 +3079,10 @@
     <t>（贺年明信片）</t>
   </si>
   <si>
-    <t>節約</t>
-  </si>
-  <si>
-    <t>せつやく</t>
+    <t>倹約</t>
+  </si>
+  <si>
+    <t>けんやく</t>
   </si>
   <si>
     <t>年賀状</t>
@@ -3056,10 +3091,10 @@
     <t>ねんがじょう</t>
   </si>
   <si>
-    <t>倹約</t>
-  </si>
-  <si>
-    <t>けんやく</t>
+    <t>備蓄</t>
+  </si>
+  <si>
+    <t>びちく</t>
   </si>
   <si>
     <t>宅急便</t>
@@ -3068,10 +3103,10 @@
     <t>たっきゅびん</t>
   </si>
   <si>
-    <t>備蓄</t>
-  </si>
-  <si>
-    <t>びちく</t>
+    <t>備蓄品</t>
+  </si>
+  <si>
+    <t>びちくひん</t>
   </si>
   <si>
     <t>皿</t>
@@ -3083,10 +3118,13 @@
     <t>（烟灰缸）</t>
   </si>
   <si>
-    <t>備蓄品</t>
-  </si>
-  <si>
-    <t>びちくひん</t>
+    <t>お決まり</t>
+  </si>
+  <si>
+    <t>おきまり</t>
+  </si>
+  <si>
+    <t>（惯例，老习惯）</t>
   </si>
   <si>
     <t>灰皿</t>
@@ -3095,13 +3133,13 @@
     <t>はいざら</t>
   </si>
   <si>
-    <t>お決まり</t>
-  </si>
-  <si>
-    <t>おきまり</t>
-  </si>
-  <si>
-    <t>（惯例，老习惯）</t>
+    <t>墓参り</t>
+  </si>
+  <si>
+    <t>はかまいり</t>
+  </si>
+  <si>
+    <t>（上坟）</t>
   </si>
   <si>
     <t>通帳</t>
@@ -3168,6 +3206,15 @@
   </si>
   <si>
     <t>てほん</t>
+  </si>
+  <si>
+    <t>宝くじ</t>
+  </si>
+  <si>
+    <t>たからくじ</t>
+  </si>
+  <si>
+    <t>（彩票，抽奖券）</t>
   </si>
   <si>
     <t>芸</t>
@@ -4435,7 +4482,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4494,9 +4541,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4817,7 +4861,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:N30"/>
+  <dimension ref="A2:N33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="2"/>
@@ -4851,538 +4895,544 @@
       <c r="J2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="M2"/>
+      <c r="N2"/>
     </row>
     <row r="3" ht="20.4" customHeight="1" spans="1:14">
       <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="M3"/>
+      <c r="N3"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="M4"/>
+      <c r="N4"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="M5"/>
+      <c r="N5"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M6" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="M6"/>
+      <c r="N6"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M7" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M7"/>
+      <c r="N7"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>54</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="M8"/>
+      <c r="N8"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="2" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>101</v>
+        <v>89</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>132</v>
+        <v>121</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -5410,28 +5460,28 @@
     <row r="1" s="13" customFormat="1" ht="18" spans="1:7">
       <c r="A1" s="15"/>
       <c r="B1" s="15" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G1" s="15"/>
     </row>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E2" s="16"/>
       <c r="F2" s="16"/>
@@ -5439,48 +5489,48 @@
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="16" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
     </row>
     <row r="4" ht="19.8" spans="1:7">
       <c r="A4" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>168</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>172</v>
       </c>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
     </row>
     <row r="5" ht="36" spans="1:7">
       <c r="A5" s="16" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
@@ -5488,32 +5538,32 @@
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>177</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>181</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
     </row>
     <row r="7" ht="36" spans="1:7">
       <c r="A7" s="16" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -5522,13 +5572,13 @@
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
@@ -5537,32 +5587,32 @@
     </row>
     <row r="9" ht="19.8" spans="1:7">
       <c r="A9" s="17" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="17" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" ht="19.8" spans="1:7">
       <c r="A10" s="17" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="16"/>
@@ -5571,25 +5621,25 @@
     </row>
     <row r="11" ht="19.8" spans="1:7">
       <c r="A11" s="17" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B11" s="19"/>
       <c r="D11" s="21" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="16"/>
     </row>
     <row r="12" ht="19.8" spans="1:7">
       <c r="A12" s="17" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B12" s="19"/>
       <c r="D12" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="17"/>
@@ -5597,47 +5647,47 @@
     </row>
     <row r="13" ht="19.8" spans="1:7">
       <c r="A13" s="17" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F13" s="17"/>
       <c r="G13" s="16"/>
     </row>
     <row r="14" ht="19.8" spans="1:7">
       <c r="A14" s="17" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="20"/>
       <c r="D14" s="24" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="16"/>
     </row>
     <row r="15" ht="19.8" spans="1:7">
       <c r="A15" s="17" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="20"/>
       <c r="D15" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="16"/>
@@ -5653,132 +5703,132 @@
     </row>
     <row r="17" ht="19.8" spans="1:7">
       <c r="A17" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>211</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>215</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="16"/>
     </row>
     <row r="18" ht="43.2" spans="1:7">
       <c r="A18" s="17" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="20"/>
       <c r="D18" s="24" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="16"/>
     </row>
     <row r="19" ht="19.8" spans="1:7">
       <c r="A19" s="17" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="16"/>
     </row>
     <row r="20" ht="19.8" spans="1:7">
       <c r="A20" s="17" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="16"/>
     </row>
     <row r="21" ht="19.8" spans="1:7">
       <c r="A21" s="17" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="16"/>
     </row>
     <row r="22" ht="24" spans="1:7">
       <c r="A22" s="16" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:7">
       <c r="A23" s="16" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
     </row>
     <row r="24" ht="18" spans="1:7">
       <c r="A24" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
     </row>
     <row r="25" ht="18" spans="1:7">
       <c r="A25" s="16" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
@@ -5786,32 +5836,32 @@
     </row>
     <row r="26" ht="72" spans="1:7">
       <c r="A26" s="16" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
     </row>
     <row r="27" ht="18" spans="1:7">
       <c r="A27" s="16" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
@@ -5820,13 +5870,13 @@
     </row>
     <row r="28" ht="18" spans="1:7">
       <c r="A28" s="16" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
@@ -5835,26 +5885,26 @@
     </row>
     <row r="29" ht="18" spans="1:7">
       <c r="A29" s="16" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E29" s="16"/>
       <c r="F29" s="25" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G29" s="16"/>
     </row>
     <row r="30" ht="18" spans="1:7">
       <c r="A30" s="29" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -5865,76 +5915,76 @@
     </row>
     <row r="31" ht="18" spans="1:7">
       <c r="A31" s="16" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="25" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:7">
       <c r="A32" s="30" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="16"/>
       <c r="D32" s="25" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F32" s="25"/>
       <c r="G32" s="25"/>
     </row>
     <row r="33" ht="18" spans="1:7">
       <c r="A33" s="31" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C33" s="16"/>
       <c r="D33" s="25" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F33" s="25"/>
       <c r="G33" s="25"/>
     </row>
     <row r="34" ht="18" spans="1:7">
       <c r="A34" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B34" s="16"/>
       <c r="D34" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F34" s="16"/>
       <c r="G34" s="16"/>
     </row>
     <row r="35" ht="18" spans="1:7">
       <c r="A35" s="16" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
       <c r="D35" s="16" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
@@ -5942,7 +5992,7 @@
     </row>
     <row r="36" ht="18" spans="1:7">
       <c r="A36" s="16" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -5953,12 +6003,12 @@
     </row>
     <row r="37" ht="18" spans="1:7">
       <c r="A37" s="32" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
       <c r="D37" s="33" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E37" s="16"/>
       <c r="F37" s="16"/>
@@ -5966,45 +6016,45 @@
     </row>
     <row r="38" ht="18" spans="1:7">
       <c r="A38" s="16" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
       <c r="D38" s="7" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E38" s="16"/>
       <c r="F38" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G38" s="16"/>
     </row>
     <row r="39" ht="18" spans="1:7">
       <c r="A39" s="16" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
       <c r="D39" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G39" s="16"/>
     </row>
     <row r="40" ht="18" spans="1:7">
       <c r="A40" s="16" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="16"/>
@@ -6013,10 +6063,10 @@
     </row>
     <row r="41" ht="18" spans="1:7">
       <c r="A41" s="16" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
@@ -6026,10 +6076,10 @@
     </row>
     <row r="42" ht="18" spans="1:7">
       <c r="A42" s="16" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
@@ -6039,7 +6089,7 @@
     </row>
     <row r="43" ht="18" spans="1:7">
       <c r="A43" s="16" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B43" s="16"/>
       <c r="D43" s="16"/>
@@ -6049,7 +6099,7 @@
     </row>
     <row r="44" ht="18" spans="1:7">
       <c r="A44" s="16" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B44" s="16"/>
       <c r="D44" s="16"/>
@@ -6059,83 +6109,83 @@
     </row>
     <row r="45" ht="18" spans="1:7">
       <c r="A45" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E45" s="16" t="s">
         <v>294</v>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>298</v>
       </c>
       <c r="F45" s="16"/>
       <c r="G45" s="16"/>
     </row>
     <row r="46" ht="43.2" spans="1:7">
       <c r="A46" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="D46" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="E46" s="16" t="s">
         <v>299</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C46" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="D46" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>303</v>
       </c>
       <c r="F46" s="16"/>
       <c r="G46" s="16"/>
     </row>
     <row r="47" ht="28.8" spans="1:7">
       <c r="A47" s="16" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
       <c r="D47" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G47" s="25" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:7">
       <c r="A48" s="16" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
       <c r="D48" s="4"/>
       <c r="E48" s="25" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="25"/>
     </row>
     <row r="49" ht="36" spans="1:7">
       <c r="A49" s="16" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="25"/>
@@ -6144,13 +6194,13 @@
     </row>
     <row r="50" ht="36" spans="1:7">
       <c r="A50" s="7" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="16"/>
@@ -6159,7 +6209,7 @@
     </row>
     <row r="51" ht="18" spans="1:7">
       <c r="A51" s="16" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -6170,7 +6220,7 @@
     </row>
     <row r="52" ht="18" spans="1:7">
       <c r="A52" s="16" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -6181,7 +6231,7 @@
     </row>
     <row r="53" ht="18" spans="1:7">
       <c r="A53" s="16" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -6192,24 +6242,24 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="14" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:7">
       <c r="A55" s="16" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="16"/>
@@ -6218,13 +6268,13 @@
     </row>
     <row r="56" ht="18" spans="1:7">
       <c r="A56" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="16"/>
@@ -6233,54 +6283,54 @@
     </row>
     <row r="57" ht="36" spans="1:7">
       <c r="A57" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="E57" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="F57" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="G57" s="7" t="s">
         <v>329</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:7">
       <c r="A58" s="16" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B58" s="34" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D58" s="33" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F58" s="16"/>
       <c r="G58" s="16"/>
     </row>
     <row r="59" ht="18" spans="1:7">
       <c r="A59" s="16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B59" s="34"/>
       <c r="C59" s="16"/>
       <c r="D59" s="16" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
@@ -6288,12 +6338,12 @@
     </row>
     <row r="60" ht="18" spans="1:7">
       <c r="A60" s="16" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B60" s="34"/>
       <c r="C60" s="16"/>
       <c r="D60" s="16" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
@@ -6301,42 +6351,42 @@
     </row>
     <row r="61" ht="18" spans="1:7">
       <c r="A61" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B61" s="34"/>
       <c r="C61" s="16"/>
       <c r="D61" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F61" s="16"/>
       <c r="G61" s="16"/>
     </row>
     <row r="62" ht="18" spans="1:7">
       <c r="A62" s="7" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B62" s="34"/>
       <c r="C62" s="16"/>
       <c r="D62" s="16" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F62" s="16"/>
       <c r="G62" s="16"/>
     </row>
     <row r="63" ht="18" hidden="1" spans="1:7">
       <c r="A63" s="16" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B63" s="34"/>
       <c r="C63" s="16"/>
       <c r="D63" s="16" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
@@ -6344,13 +6394,13 @@
     </row>
     <row r="64" ht="36" spans="1:7">
       <c r="A64" s="35" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B64" s="35" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
@@ -6359,13 +6409,13 @@
     </row>
     <row r="65" ht="18" spans="1:7">
       <c r="A65" s="16" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
@@ -6374,13 +6424,13 @@
     </row>
     <row r="66" ht="18" spans="1:7">
       <c r="A66" s="16" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="16"/>
@@ -6389,13 +6439,13 @@
     </row>
     <row r="67" ht="36" spans="1:7">
       <c r="A67" s="16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B67" s="34" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D67" s="16"/>
       <c r="E67" s="16"/>
@@ -6404,16 +6454,16 @@
     </row>
     <row r="68" ht="18" spans="1:7">
       <c r="A68" s="16" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B68" s="32" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C68" s="32" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E68" s="16"/>
       <c r="F68" s="16"/>
@@ -6421,12 +6471,12 @@
     </row>
     <row r="69" ht="18" spans="1:7">
       <c r="A69" s="16" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
       <c r="D69" s="16" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E69" s="16"/>
       <c r="F69" s="16"/>
@@ -6434,16 +6484,16 @@
     </row>
     <row r="70" ht="19.8" spans="1:7">
       <c r="A70" s="16" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E70" s="16"/>
       <c r="F70" s="16"/>
@@ -6451,33 +6501,33 @@
     </row>
     <row r="71" ht="36" spans="1:7">
       <c r="A71" s="16" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>371</v>
+        <v>96</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F71" s="16"/>
       <c r="G71" s="16"/>
     </row>
     <row r="72" ht="19.8" spans="1:7">
       <c r="A72" s="16" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>371</v>
+        <v>96</v>
       </c>
       <c r="C72" s="16"/>
       <c r="D72" s="17" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E72" s="17"/>
       <c r="F72" s="16"/>
@@ -6485,10 +6535,10 @@
     </row>
     <row r="73" ht="19.8" spans="1:7">
       <c r="A73" s="16" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>371</v>
+        <v>96</v>
       </c>
       <c r="C73" s="16"/>
       <c r="D73" s="17"/>
@@ -6498,50 +6548,50 @@
     </row>
     <row r="74" ht="19.8" spans="1:7">
       <c r="A74" s="16" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>371</v>
+        <v>96</v>
       </c>
       <c r="C74" s="16"/>
       <c r="D74" s="34" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E74" s="17"/>
       <c r="F74" s="24" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="75" ht="19.8" spans="1:7">
       <c r="A75" s="16" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>371</v>
+        <v>96</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D75" s="34" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G75" s="16"/>
     </row>
     <row r="76" ht="19.8" spans="1:7">
       <c r="A76" s="16" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>371</v>
+        <v>96</v>
       </c>
       <c r="C76" s="16"/>
       <c r="D76" s="17"/>
@@ -6551,10 +6601,10 @@
     </row>
     <row r="77" ht="19.8" spans="1:7">
       <c r="A77" s="16" t="s">
-        <v>387</v>
+        <v>95</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>371</v>
+        <v>96</v>
       </c>
       <c r="C77" s="16"/>
       <c r="D77" s="17"/>
@@ -6564,13 +6614,13 @@
     </row>
     <row r="78" ht="36" spans="1:7">
       <c r="A78" s="16" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D78" s="17"/>
       <c r="E78" s="17"/>
@@ -6579,32 +6629,32 @@
     </row>
     <row r="79" ht="18" spans="1:7">
       <c r="A79" s="16" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="F79" s="16"/>
       <c r="G79" s="16"/>
     </row>
     <row r="80" ht="19.8" spans="1:7">
       <c r="A80" s="17" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D80" s="16"/>
       <c r="E80" s="16"/>
@@ -6613,13 +6663,13 @@
     </row>
     <row r="81" ht="19.8" spans="1:7">
       <c r="A81" s="17" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D81" s="16"/>
       <c r="E81" s="16"/>
@@ -6628,13 +6678,13 @@
     </row>
     <row r="82" ht="18" spans="1:7">
       <c r="A82" s="16" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D82" s="16"/>
       <c r="E82" s="16"/>
@@ -6643,44 +6693,44 @@
     </row>
     <row r="83" ht="36" spans="1:7">
       <c r="A83" s="32" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
       <c r="D83" s="33" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E83" s="36" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="F83" s="16"/>
       <c r="G83" s="16"/>
     </row>
     <row r="84" ht="18" spans="1:7">
       <c r="A84" s="32" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="D84" s="34" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="E84" s="32" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="F84" s="16"/>
       <c r="G84" s="16"/>
     </row>
     <row r="85" ht="18" spans="1:7">
       <c r="A85" s="32" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C85" s="32" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D85" s="24" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="E85" s="16"/>
       <c r="F85" s="16"/>
@@ -6688,56 +6738,56 @@
     </row>
     <row r="86" ht="18" spans="1:7">
       <c r="A86" s="16" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B86" s="16"/>
       <c r="D86" s="16" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E86" s="37" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="F86" s="16"/>
       <c r="G86" s="16"/>
     </row>
     <row r="87" ht="18" spans="1:7">
       <c r="A87" s="16" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B87" s="16"/>
       <c r="C87" s="16"/>
       <c r="D87" s="16" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="F87" s="16"/>
       <c r="G87" s="16"/>
     </row>
     <row r="88" ht="18" spans="1:7">
       <c r="A88" s="16" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
       <c r="D88" s="16" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="F88" s="16"/>
       <c r="G88" s="16"/>
     </row>
     <row r="89" ht="18" spans="1:7">
       <c r="A89" s="16" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B89" s="16"/>
       <c r="C89" s="16"/>
       <c r="D89" s="38" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="E89" s="16"/>
       <c r="F89" s="16"/>
@@ -6745,42 +6795,42 @@
     </row>
     <row r="90" ht="36" spans="1:7">
       <c r="A90" s="16" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C90" s="18" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
     </row>
     <row r="91" ht="18" spans="1:7">
       <c r="A91" s="16" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B91" s="16"/>
       <c r="C91" s="16"/>
       <c r="D91" s="16" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E91" s="16"/>
       <c r="F91" s="4" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="92" ht="18" spans="1:7">
       <c r="A92" s="16" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B92" s="16"/>
       <c r="C92" s="16"/>
       <c r="D92" s="16" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E92" s="16"/>
       <c r="F92" s="16"/>
@@ -6788,60 +6838,60 @@
     </row>
     <row r="93" ht="18" spans="1:7">
       <c r="A93" s="16" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B93" s="16"/>
       <c r="C93" s="16"/>
       <c r="D93" s="16" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="F93" s="16"/>
       <c r="G93" s="16"/>
     </row>
     <row r="94" ht="18" spans="1:7">
       <c r="A94" s="16" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B94" s="16"/>
       <c r="C94" s="16"/>
       <c r="D94" s="39" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="F94" s="16"/>
       <c r="G94" s="16"/>
     </row>
     <row r="95" ht="19.8" spans="1:7">
       <c r="A95" s="16" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B95" s="40" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C95" s="16"/>
       <c r="D95" s="16" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="F95" s="16"/>
       <c r="G95" s="16"/>
     </row>
     <row r="96" ht="36" spans="1:7">
       <c r="A96" s="16" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D96" s="16"/>
       <c r="E96" s="16"/>
@@ -6850,12 +6900,12 @@
     </row>
     <row r="97" ht="18" spans="1:7">
       <c r="A97" s="19" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B97" s="16"/>
       <c r="C97" s="16"/>
       <c r="D97" s="19" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="E97" s="16"/>
       <c r="F97" s="16"/>
@@ -6863,20 +6913,20 @@
     </row>
     <row r="98" ht="18" spans="1:7">
       <c r="A98" s="16" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C98" s="16"/>
       <c r="D98" s="34" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="G98" s="16"/>
     </row>
@@ -6900,309 +6950,309 @@
   <sheetData>
     <row r="1" ht="18" spans="1:13">
       <c r="I1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="L1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:13">
       <c r="A2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="K2" t="s">
         <v>451</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="K2" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:13">
       <c r="A3" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B3" t="s">
+        <v>453</v>
+      </c>
+      <c r="E3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="G3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="K3" t="s">
         <v>458</v>
-      </c>
-      <c r="B3" t="s">
-        <v>459</v>
-      </c>
-      <c r="E3" t="s">
-        <v>460</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="G3" t="s">
-        <v>461</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="K3" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:13">
       <c r="A4" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="G4" t="s">
+        <v>463</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G4" t="s">
-        <v>469</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E5" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:13">
       <c r="E6" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:13">
       <c r="A7" t="s">
+        <v>477</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:13">
       <c r="A8" t="s">
+        <v>484</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E8" t="s">
+        <v>487</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E8" t="s">
-        <v>493</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:13">
       <c r="A9" t="s">
+        <v>492</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:13">
       <c r="A10" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C10" t="s">
+        <v>501</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C10" t="s">
-        <v>507</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="C11" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="I11" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C14" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="K14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" ht="18" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="C16" s="12"/>
       <c r="I16" s="2"/>
@@ -7210,10 +7260,10 @@
     </row>
     <row r="17" ht="18" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="C17" s="12"/>
       <c r="I17" s="2"/>
@@ -7225,68 +7275,68 @@
     </row>
     <row r="19" ht="18" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:10">
       <c r="A20" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>
@@ -7311,677 +7361,689 @@
   <sheetData>
     <row r="1" ht="18" spans="1:20">
       <c r="A1" s="2" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:20">
       <c r="A2" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="G2" t="s">
+        <v>557</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="I2" t="s">
         <v>559</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="K2" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="L2" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="O2" t="s">
         <v>562</v>
       </c>
-      <c r="G2" t="s">
+      <c r="P2" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="I2" t="s">
-        <v>565</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="O2" t="s">
-        <v>568</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="S2" s="2" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:20">
       <c r="A3" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="G3" t="s">
+        <v>568</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="L3" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="O3" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="P3" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="G3" t="s">
-        <v>574</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:20">
       <c r="A4" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="G4" t="s">
+        <v>578</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="K4" t="s">
+        <v>580</v>
+      </c>
+      <c r="L4" t="s">
+        <v>581</v>
+      </c>
+      <c r="M4" t="s">
         <v>582</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="O4" t="s">
         <v>583</v>
       </c>
-      <c r="G4" t="s">
+      <c r="P4" t="s">
         <v>584</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="K4" t="s">
-        <v>586</v>
-      </c>
-      <c r="L4" t="s">
-        <v>587</v>
-      </c>
-      <c r="M4" t="s">
-        <v>588</v>
-      </c>
-      <c r="O4" t="s">
-        <v>589</v>
-      </c>
-      <c r="P4" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:20">
       <c r="A5" t="s">
+        <v>585</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>593</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:20">
       <c r="A6" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="G6" t="s">
+        <v>598</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="L6" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="G6" t="s">
-        <v>604</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:20">
       <c r="A7" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>607</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="L7" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="O7" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="P7" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="Q7" t="s">
         <v>614</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>620</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:20">
       <c r="A8" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="G8" t="s">
+        <v>620</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="K8" t="s">
         <v>622</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="L8" t="s">
         <v>623</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="G8" t="s">
-        <v>626</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="K8" t="s">
-        <v>628</v>
-      </c>
-      <c r="L8" t="s">
-        <v>629</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:20">
       <c r="A9" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="G9" t="s">
+        <v>630</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="K9" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="G9" t="s">
+      <c r="P9" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:20">
       <c r="A10" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B10" t="s">
+        <v>638</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="I10" t="s">
         <v>643</v>
       </c>
-      <c r="B10" t="s">
+      <c r="K10" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="I10" t="s">
-        <v>649</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:20">
       <c r="A11" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="I11" t="s">
+        <v>652</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="Q11" t="s">
         <v>657</v>
-      </c>
-      <c r="I11" t="s">
-        <v>658</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:20">
       <c r="A12" s="8" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="I12" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:20">
       <c r="A13" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="Q13" t="s">
         <v>670</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:20">
       <c r="A14" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="Q14" t="s">
         <v>677</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>679</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>680</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:20">
       <c r="A15" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:20">
       <c r="A16" s="10" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="O16" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="A17" s="10" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="P18" s="2" t="s">
         <v>702</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="A19" s="2" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="G19" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="H19" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="A20" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C20" t="s">
+        <v>711</v>
+      </c>
+      <c r="G20" t="s">
+        <v>712</v>
+      </c>
+      <c r="H20" t="s">
+        <v>713</v>
+      </c>
+      <c r="O20" t="s">
+        <v>714</v>
+      </c>
+      <c r="P20" t="s">
         <v>715</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="C20" t="s">
-        <v>717</v>
-      </c>
-      <c r="G20" t="s">
-        <v>718</v>
-      </c>
-      <c r="H20" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
       <c r="A21" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
+      </c>
+      <c r="O21" t="s">
+        <v>718</v>
+      </c>
+      <c r="P21" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="A26" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="A27" s="11" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="A28" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C28" t="s">
         <v>734</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="E28" t="s">
         <v>735</v>
-      </c>
-      <c r="C28" t="s">
-        <v>736</v>
-      </c>
-      <c r="E28" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="A29" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="C29" t="s">
         <v>737</v>
-      </c>
-      <c r="C29" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="A30" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
       <c r="A31" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:2">
       <c r="A33" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
   </sheetData>
@@ -7993,7 +8055,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G22"/>
+  <dimension ref="A2:G24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -8003,281 +8065,287 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>752</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>755</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="D4" t="s">
         <v>756</v>
       </c>
-      <c r="C4" s="6" t="s">
+    </row>
+    <row r="5" ht="18" spans="1:7">
+      <c r="A5" t="s">
         <v>757</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B5" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="5" ht="18" spans="1:7">
-      <c r="A5" s="2" t="s">
+      <c r="D5" t="s">
         <v>759</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="D5" t="s">
-        <v>761</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="D6" t="s">
         <v>763</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F9" s="2" t="s">
         <v>782</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C10" t="s">
+        <v>785</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C11" t="s">
+        <v>791</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="C11" t="s">
-        <v>794</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C12" t="s">
+        <v>796</v>
+      </c>
+      <c r="D12" t="s">
         <v>797</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="E12" t="s">
         <v>798</v>
-      </c>
-      <c r="D12" t="s">
-        <v>799</v>
-      </c>
-      <c r="E12" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="C14" t="s">
-        <v>807</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C15" t="s">
+        <v>809</v>
+      </c>
+      <c r="D15" t="s">
         <v>810</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="E15" t="s">
         <v>811</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>812</v>
       </c>
-      <c r="E15" t="s">
+    </row>
+    <row r="16" ht="18" spans="1:7">
+      <c r="A16" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="F15" t="s">
+      <c r="B16" s="2" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="16" ht="15.6" spans="1:7">
-      <c r="A16" s="7" t="s">
+      <c r="D16" t="s">
         <v>815</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="E16" t="s">
         <v>816</v>
+      </c>
+      <c r="F16" t="s">
+        <v>817</v>
       </c>
     </row>
     <row r="17" ht="15.6" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="18" ht="18" spans="1:3">
-      <c r="A18" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="B18" s="2" t="s">
+    </row>
+    <row r="18" ht="15.6" spans="1:3">
+      <c r="A18" s="7" t="s">
         <v>820</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>821</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="C20" s="6" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
+    <row r="21" ht="18" spans="1:3">
+      <c r="A21" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="6" t="s">
         <v>828</v>
       </c>
     </row>
@@ -8287,6 +8355,28 @@
       </c>
       <c r="B22" t="s">
         <v>830</v>
+      </c>
+      <c r="C22" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>832</v>
+      </c>
+      <c r="B23" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>834</v>
+      </c>
+      <c r="B24" t="s">
+        <v>835</v>
+      </c>
+      <c r="C24" t="s">
+        <v>836</v>
       </c>
     </row>
   </sheetData>
@@ -8309,306 +8399,306 @@
   <sheetData>
     <row r="2" ht="18" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="K2" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="L2" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="K3" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="C4" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="H4" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" ht="18" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="G18" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -8648,237 +8738,237 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
     </row>
   </sheetData>
@@ -8898,10 +8988,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
     </row>
   </sheetData>

--- a/Words(音读音 & 训练音).xlsx
+++ b/Words(音读音 & 训练音).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Object(もの)" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="999">
   <si>
     <t>名称</t>
   </si>
@@ -669,34 +669,31 @@
     <t>つかいみち</t>
   </si>
   <si>
+    <t>事柄</t>
+  </si>
+  <si>
+    <t>ことがら</t>
+  </si>
+  <si>
     <t>通用</t>
   </si>
   <si>
     <t>つうよう</t>
   </si>
   <si>
+    <t>要件</t>
+  </si>
+  <si>
+    <t>ようけん</t>
+  </si>
+  <si>
+    <t>（事情）</t>
+  </si>
+  <si>
     <t>主題</t>
   </si>
   <si>
     <t>しゅだい</t>
-  </si>
-  <si>
-    <t>理</t>
-  </si>
-  <si>
-    <t>ことわり</t>
-  </si>
-  <si>
-    <t>質量</t>
-  </si>
-  <si>
-    <t>しつりょ</t>
-  </si>
-  <si>
-    <t>標準</t>
-  </si>
-  <si>
-    <t>ひょうじゅん</t>
   </si>
   <si>
     <t>奇妙</t>
@@ -740,6 +737,12 @@
     </r>
   </si>
   <si>
+    <t>理</t>
+  </si>
+  <si>
+    <t>ことわり</t>
+  </si>
+  <si>
     <t>見事</t>
   </si>
   <si>
@@ -764,6 +767,18 @@
       </rPr>
       <t>丽）</t>
     </r>
+  </si>
+  <si>
+    <t>質量</t>
+  </si>
+  <si>
+    <t>しつりょ</t>
+  </si>
+  <si>
+    <t>標準</t>
+  </si>
+  <si>
+    <t>ひょうじゅん</t>
   </si>
   <si>
     <t>音读</t>
@@ -1962,6 +1977,15 @@
     <t>（公文包）</t>
   </si>
   <si>
+    <t>フリーサイズ</t>
+  </si>
+  <si>
+    <t>freesize</t>
+  </si>
+  <si>
+    <t>（均码）</t>
+  </si>
+  <si>
     <t>正方形</t>
   </si>
   <si>
@@ -2135,6 +2159,15 @@
       </rPr>
       <t>鞋带）</t>
     </r>
+  </si>
+  <si>
+    <t>櫛</t>
+  </si>
+  <si>
+    <t>くし</t>
+  </si>
+  <si>
+    <t>（梳子）</t>
   </si>
   <si>
     <t>食品</t>
@@ -2601,22 +2634,40 @@
     <t>せっしゅ</t>
   </si>
   <si>
+    <t>うお</t>
+  </si>
+  <si>
+    <t>伝統食品</t>
+  </si>
+  <si>
+    <t>でんとうしょくひん</t>
+  </si>
+  <si>
+    <t>加工</t>
+  </si>
+  <si>
+    <t>かこう</t>
+  </si>
+  <si>
     <t>煮魚</t>
   </si>
   <si>
     <t>にざかな</t>
   </si>
   <si>
-    <t>伝統食品</t>
-  </si>
-  <si>
-    <t>でんとうしょくひん</t>
-  </si>
-  <si>
-    <t>加工</t>
-  </si>
-  <si>
-    <t>かこう</t>
+    <t>（刺し身）</t>
+  </si>
+  <si>
+    <t>朝ご飯</t>
+  </si>
+  <si>
+    <t>あさごはん</t>
+  </si>
+  <si>
+    <t>濾過</t>
+  </si>
+  <si>
+    <t>ろか</t>
   </si>
   <si>
     <t>刺身</t>
@@ -2625,19 +2676,16 @@
     <t>さしみ</t>
   </si>
   <si>
-    <t>（刺し身）</t>
-  </si>
-  <si>
-    <t>朝ご飯</t>
-  </si>
-  <si>
-    <t>あさごはん</t>
-  </si>
-  <si>
-    <t>濾過</t>
-  </si>
-  <si>
-    <t>ろか</t>
+    <t>夕飯</t>
+  </si>
+  <si>
+    <t>ゆうはん</t>
+  </si>
+  <si>
+    <t>舐める</t>
+  </si>
+  <si>
+    <t>なめる</t>
   </si>
   <si>
     <t>煮干し</t>
@@ -2663,16 +2711,19 @@
     </r>
   </si>
   <si>
-    <t>夕飯</t>
-  </si>
-  <si>
-    <t>ゆうはん</t>
-  </si>
-  <si>
-    <t>舐める</t>
-  </si>
-  <si>
-    <t>なめる</t>
+    <t>（红芋）</t>
+  </si>
+  <si>
+    <t>晩御飯</t>
+  </si>
+  <si>
+    <t>ばんごはん</t>
+  </si>
+  <si>
+    <t>熱する</t>
+  </si>
+  <si>
+    <t>ねっする</t>
   </si>
   <si>
     <t>薩摩芋</t>
@@ -2681,19 +2732,10 @@
     <t>さつまいも</t>
   </si>
   <si>
-    <t>（红芋）</t>
-  </si>
-  <si>
-    <t>晩御飯</t>
-  </si>
-  <si>
-    <t>ばんごはん</t>
-  </si>
-  <si>
-    <t>熱する</t>
-  </si>
-  <si>
-    <t>ねっする</t>
+    <t>冷たくなる</t>
+  </si>
+  <si>
+    <t>つめたくなる</t>
   </si>
   <si>
     <t>鰻</t>
@@ -2702,12 +2744,6 @@
     <t>うなぎ</t>
   </si>
   <si>
-    <t>冷たくなる</t>
-  </si>
-  <si>
-    <t>つめたくなる</t>
-  </si>
-  <si>
     <t>鰻丼</t>
   </si>
   <si>
@@ -2744,22 +2780,22 @@
     <t>おでん</t>
   </si>
   <si>
+    <t>（鸡翅膀）</t>
+  </si>
+  <si>
+    <t>からあげぼう</t>
+  </si>
+  <si>
     <t>手羽先</t>
   </si>
   <si>
     <t>てばさき</t>
   </si>
   <si>
-    <t>（鸡翅膀）</t>
-  </si>
-  <si>
-    <t>からあげぼう</t>
+    <t>（炸鸡翅）</t>
   </si>
   <si>
     <t>唐揚げ棒</t>
-  </si>
-  <si>
-    <t>（炸鸡翅）</t>
   </si>
   <si>
     <t>もんじゃ焼</t>
@@ -3217,6 +3253,15 @@
     <t>（彩票，抽奖券）</t>
   </si>
   <si>
+    <t>整髪料</t>
+  </si>
+  <si>
+    <t>せいはつりょう</t>
+  </si>
+  <si>
+    <t>（洗发水）</t>
+  </si>
+  <si>
     <t>芸</t>
   </si>
   <si>
@@ -3495,6 +3540,9 @@
     <t>みょうじょうだんたい</t>
   </si>
   <si>
+    <t>読書感想｜どくしょかんそう</t>
+  </si>
+  <si>
     <t>千と千尋</t>
   </si>
   <si>
@@ -3658,6 +3706,12 @@
   </si>
   <si>
     <t>どうわ</t>
+  </si>
+  <si>
+    <t>園芸</t>
+  </si>
+  <si>
+    <t>えんげい</t>
   </si>
   <si>
     <t>JIPT汉字整理</t>
@@ -3676,7 +3730,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="55">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3745,6 +3799,12 @@
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="Yu Gothic"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
       <charset val="128"/>
     </font>
     <font>
@@ -4024,16 +4084,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF3A3A3A"/>
       <name val="Segoe UI Symbol"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="33">
@@ -4355,13 +4415,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4370,119 +4427,122 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4501,45 +4561,46 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4861,7 +4922,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:N33"/>
+  <dimension ref="A2:N29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="2"/>
@@ -5356,21 +5417,42 @@
       <c r="B23" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="E23" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -5380,59 +5462,47 @@
       <c r="B26" s="2" t="s">
         <v>103</v>
       </c>
+      <c r="E26" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -5447,1488 +5517,1488 @@
   <dimension ref="A1:G98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="14"/>
-    <col min="2" max="2" width="11.1111111111111" style="14" customWidth="1"/>
-    <col min="3" max="3" width="28.6666666666667" style="14" customWidth="1"/>
-    <col min="4" max="4" width="8.88888888888889" style="14"/>
-    <col min="5" max="5" width="27.5555555555556" style="14" customWidth="1"/>
-    <col min="6" max="6" width="20.4444444444444" style="14" customWidth="1"/>
-    <col min="7" max="7" width="31.4444444444444" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="8.88888888888889" style="14"/>
+    <col min="1" max="1" width="8.88888888888889" style="15"/>
+    <col min="2" max="2" width="11.1111111111111" style="15" customWidth="1"/>
+    <col min="3" max="3" width="28.6666666666667" style="15" customWidth="1"/>
+    <col min="4" max="4" width="8.88888888888889" style="15"/>
+    <col min="5" max="5" width="27.5555555555556" style="15" customWidth="1"/>
+    <col min="6" max="6" width="20.4444444444444" style="15" customWidth="1"/>
+    <col min="7" max="7" width="31.4444444444444" style="15" customWidth="1"/>
+    <col min="8" max="16384" width="8.88888888888889" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" s="13" customFormat="1" ht="18" spans="1:7">
-      <c r="A1" s="15"/>
-      <c r="B1" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="G1" s="15"/>
+    <row r="1" s="14" customFormat="1" ht="18" spans="1:7">
+      <c r="A1" s="16"/>
+      <c r="B1" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" ht="18" spans="1:7">
-      <c r="A2" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="A2" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" ht="18" spans="1:7">
-      <c r="A3" s="16" t="s">
-        <v>161</v>
+      <c r="A3" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+        <v>168</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" ht="19.8" spans="1:7">
-      <c r="A4" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="A4" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" ht="36" spans="1:7">
-      <c r="A5" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="A5" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="6" ht="36" spans="1:7">
-      <c r="A6" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>175</v>
+      <c r="A6" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>180</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+        <v>181</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
     </row>
     <row r="7" ht="36" spans="1:7">
-      <c r="A7" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
+      <c r="A7" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" ht="18" spans="1:7">
-      <c r="A8" s="16" t="s">
-        <v>181</v>
+      <c r="A8" s="17" t="s">
+        <v>186</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
+        <v>188</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
     </row>
     <row r="9" ht="19.8" spans="1:7">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" ht="19.8" spans="1:7">
+      <c r="A10" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" s="18"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" ht="19.8" spans="1:7">
+      <c r="A11" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="D11" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="F11" s="24"/>
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" ht="19.8" spans="1:7">
+      <c r="A12" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="D12" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="23"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" ht="19.8" spans="1:7">
+      <c r="A13" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="17"/>
+    </row>
+    <row r="14" ht="19.8" spans="1:7">
+      <c r="A14" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="18"/>
+      <c r="G14" s="17"/>
+    </row>
+    <row r="15" ht="19.8" spans="1:7">
+      <c r="A15" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="17"/>
+    </row>
+    <row r="16" ht="19.8" spans="1:7">
+      <c r="A16" s="18"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="17"/>
+    </row>
+    <row r="17" ht="19.8" spans="1:7">
+      <c r="A17" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="17"/>
+    </row>
+    <row r="18" ht="43.2" spans="1:7">
+      <c r="A18" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="17"/>
+    </row>
+    <row r="19" ht="19.8" spans="1:7">
+      <c r="A19" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="17"/>
+    </row>
+    <row r="20" ht="19.8" spans="1:7">
+      <c r="A20" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="F20" s="18"/>
+      <c r="G20" s="17"/>
+    </row>
+    <row r="21" ht="19.8" spans="1:7">
+      <c r="A21" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="F21" s="18"/>
+      <c r="G21" s="17"/>
+    </row>
+    <row r="22" ht="24" spans="1:7">
+      <c r="A22" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" ht="18" spans="1:7">
+      <c r="A23" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+    </row>
+    <row r="24" ht="18" spans="1:7">
+      <c r="A24" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+    </row>
+    <row r="25" ht="18" spans="1:7">
+      <c r="A25" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+    </row>
+    <row r="26" ht="72" spans="1:7">
+      <c r="A26" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="10" ht="19.8" spans="1:7">
-      <c r="A10" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" ht="19.8" spans="1:7">
-      <c r="A11" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="D11" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" ht="19.8" spans="1:7">
-      <c r="A12" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="D12" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="16"/>
-    </row>
-    <row r="13" ht="19.8" spans="1:7">
-      <c r="A13" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="16"/>
-    </row>
-    <row r="14" ht="19.8" spans="1:7">
-      <c r="A14" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="16"/>
-    </row>
-    <row r="15" ht="19.8" spans="1:7">
-      <c r="A15" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="16"/>
-    </row>
-    <row r="16" ht="19.8" spans="1:7">
-      <c r="A16" s="17"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="16"/>
-    </row>
-    <row r="17" ht="19.8" spans="1:7">
-      <c r="A17" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="16"/>
-    </row>
-    <row r="18" ht="43.2" spans="1:7">
-      <c r="A18" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="16"/>
-    </row>
-    <row r="19" ht="19.8" spans="1:7">
-      <c r="A19" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="16"/>
-    </row>
-    <row r="20" ht="19.8" spans="1:7">
-      <c r="A20" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="16"/>
-    </row>
-    <row r="21" ht="19.8" spans="1:7">
-      <c r="A21" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="16"/>
-    </row>
-    <row r="22" ht="24" spans="1:7">
-      <c r="A22" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="G22" s="28" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="23" ht="18" spans="1:7">
-      <c r="A23" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-    </row>
-    <row r="24" ht="18" spans="1:7">
-      <c r="A24" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-    </row>
-    <row r="25" ht="18" spans="1:7">
-      <c r="A25" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-    </row>
-    <row r="26" ht="72" spans="1:7">
-      <c r="A26" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+      <c r="E26" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
     </row>
     <row r="27" ht="18" spans="1:7">
-      <c r="A27" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+      <c r="A27" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
     </row>
     <row r="28" ht="18" spans="1:7">
-      <c r="A28" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+      <c r="A28" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
     </row>
     <row r="29" ht="18" spans="1:7">
-      <c r="A29" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="25" t="s">
-        <v>252</v>
-      </c>
-      <c r="G29" s="16"/>
+      <c r="A29" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="E29" s="17"/>
+      <c r="F29" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="G29" s="17"/>
     </row>
     <row r="30" ht="18" spans="1:7">
-      <c r="A30" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="16"/>
+      <c r="A30" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="17"/>
     </row>
     <row r="31" ht="18" spans="1:7">
-      <c r="A31" s="16" t="s">
-        <v>254</v>
+      <c r="A31" s="17" t="s">
+        <v>259</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="25" t="s">
-        <v>258</v>
-      </c>
-      <c r="G31" s="25" t="s">
-        <v>259</v>
+        <v>260</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="E31" s="17"/>
+      <c r="F31" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="G31" s="26" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:7">
-      <c r="A32" s="30" t="s">
-        <v>260</v>
+      <c r="A32" s="31" t="s">
+        <v>265</v>
       </c>
       <c r="B32" s="4"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="25" t="s">
-        <v>261</v>
+      <c r="C32" s="17"/>
+      <c r="D32" s="26" t="s">
+        <v>266</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
+        <v>267</v>
+      </c>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
     </row>
     <row r="33" ht="18" spans="1:7">
-      <c r="A33" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="25" t="s">
-        <v>264</v>
+      <c r="A33" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="C33" s="17"/>
+      <c r="D33" s="26" t="s">
+        <v>269</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
+        <v>270</v>
+      </c>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" ht="18" spans="1:7">
-      <c r="A34" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="B34" s="16"/>
+      <c r="A34" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="B34" s="17"/>
       <c r="D34" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
+        <v>273</v>
+      </c>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
     </row>
     <row r="35" ht="18" spans="1:7">
-      <c r="A35" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+      <c r="A35" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
     </row>
     <row r="36" ht="18" spans="1:7">
-      <c r="A36" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+      <c r="A36" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
     </row>
     <row r="37" ht="18" spans="1:7">
-      <c r="A37" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="33" t="s">
-        <v>273</v>
-      </c>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
+      <c r="A37" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="34" t="s">
+        <v>278</v>
+      </c>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
     </row>
     <row r="38" ht="18" spans="1:7">
-      <c r="A38" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
+      <c r="A38" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
       <c r="D38" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="E38" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="E38" s="17"/>
       <c r="F38" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="G38" s="16"/>
+        <v>281</v>
+      </c>
+      <c r="G38" s="17"/>
     </row>
     <row r="39" ht="18" spans="1:7">
-      <c r="A39" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
+      <c r="A39" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
       <c r="D39" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>279</v>
+        <v>283</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>284</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="G39" s="16"/>
+        <v>285</v>
+      </c>
+      <c r="G39" s="17"/>
     </row>
     <row r="40" ht="18" spans="1:7">
-      <c r="A40" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>283</v>
+      <c r="A40" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>288</v>
       </c>
       <c r="D40" s="4"/>
-      <c r="E40" s="16"/>
+      <c r="E40" s="17"/>
       <c r="F40" s="4"/>
-      <c r="G40" s="16"/>
+      <c r="G40" s="17"/>
     </row>
     <row r="41" ht="18" spans="1:7">
-      <c r="A41" s="16" t="s">
-        <v>284</v>
+      <c r="A41" s="17" t="s">
+        <v>289</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
+        <v>290</v>
+      </c>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
     </row>
     <row r="42" ht="18" spans="1:7">
-      <c r="A42" s="16" t="s">
-        <v>286</v>
+      <c r="A42" s="17" t="s">
+        <v>291</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
+        <v>292</v>
+      </c>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
     </row>
     <row r="43" ht="18" spans="1:7">
-      <c r="A43" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
+      <c r="A43" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="B43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
     </row>
     <row r="44" ht="18" spans="1:7">
-      <c r="A44" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="B44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
+      <c r="A44" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
     </row>
     <row r="45" ht="18" spans="1:7">
-      <c r="A45" s="16" t="s">
-        <v>290</v>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
+      <c r="A45" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
     </row>
     <row r="46" ht="43.2" spans="1:7">
-      <c r="A46" s="16" t="s">
-        <v>295</v>
+      <c r="A46" s="17" t="s">
+        <v>300</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C46" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="D46" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
+        <v>301</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
     </row>
     <row r="47" ht="28.8" spans="1:7">
-      <c r="A47" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
+      <c r="A47" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
       <c r="D47" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="E47" s="27" t="s">
-        <v>302</v>
+        <v>306</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>307</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="G47" s="25" t="s">
-        <v>304</v>
+        <v>308</v>
+      </c>
+      <c r="G47" s="26" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:7">
-      <c r="A48" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
+      <c r="A48" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="25" t="s">
-        <v>306</v>
+      <c r="E48" s="26" t="s">
+        <v>311</v>
       </c>
       <c r="F48" s="4"/>
-      <c r="G48" s="25"/>
+      <c r="G48" s="26"/>
     </row>
     <row r="49" ht="36" spans="1:7">
-      <c r="A49" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="C49" s="18" t="s">
-        <v>309</v>
+      <c r="A49" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>314</v>
       </c>
       <c r="D49" s="4"/>
-      <c r="E49" s="25"/>
+      <c r="E49" s="26"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="25"/>
+      <c r="G49" s="26"/>
     </row>
     <row r="50" ht="36" spans="1:7">
       <c r="A50" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>312</v>
+        <v>315</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>317</v>
       </c>
       <c r="D50" s="4"/>
-      <c r="E50" s="16"/>
+      <c r="E50" s="17"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="25"/>
+      <c r="G50" s="26"/>
     </row>
     <row r="51" ht="18" spans="1:7">
-      <c r="A51" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
+      <c r="A51" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="16"/>
+      <c r="E51" s="17"/>
       <c r="F51" s="4"/>
-      <c r="G51" s="25"/>
+      <c r="G51" s="26"/>
     </row>
     <row r="52" ht="18" spans="1:7">
-      <c r="A52" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
+      <c r="A52" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="25"/>
+      <c r="E52" s="26"/>
       <c r="F52" s="4"/>
-      <c r="G52" s="25"/>
+      <c r="G52" s="26"/>
     </row>
     <row r="53" ht="18" spans="1:7">
-      <c r="A53" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
+      <c r="A53" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="25"/>
+      <c r="E53" s="26"/>
       <c r="F53" s="4"/>
-      <c r="G53" s="25"/>
+      <c r="G53" s="26"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="14" t="s">
-        <v>316</v>
+      <c r="A54" s="15" t="s">
+        <v>321</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>318</v>
+        <v>322</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:7">
-      <c r="A55" s="16" t="s">
-        <v>319</v>
+      <c r="A55" s="17" t="s">
+        <v>324</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>320</v>
+        <v>248</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>325</v>
       </c>
       <c r="D55" s="4"/>
-      <c r="E55" s="16"/>
+      <c r="E55" s="17"/>
       <c r="F55" s="4"/>
-      <c r="G55" s="25"/>
+      <c r="G55" s="26"/>
     </row>
     <row r="56" ht="18" spans="1:7">
       <c r="A56" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>323</v>
+        <v>326</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>328</v>
       </c>
       <c r="D56" s="4"/>
-      <c r="E56" s="16"/>
+      <c r="E56" s="17"/>
       <c r="F56" s="4"/>
-      <c r="G56" s="25"/>
+      <c r="G56" s="26"/>
     </row>
     <row r="57" ht="36" spans="1:7">
-      <c r="A57" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>328</v>
+      <c r="A57" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>333</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:7">
-      <c r="A58" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="B58" s="34" t="s">
-        <v>232</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="D58" s="33" t="s">
-        <v>332</v>
+      <c r="A58" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B58" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="D58" s="34" t="s">
+        <v>337</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
+        <v>338</v>
+      </c>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
     </row>
     <row r="59" ht="18" spans="1:7">
-      <c r="A59" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="B59" s="34"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
+      <c r="A59" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="B59" s="35"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
     </row>
     <row r="60" ht="18" spans="1:7">
-      <c r="A60" s="16" t="s">
-        <v>336</v>
-      </c>
-      <c r="B60" s="34"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
+      <c r="A60" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B60" s="35"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
     </row>
     <row r="61" ht="18" spans="1:7">
-      <c r="A61" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="B61" s="34"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16" t="s">
-        <v>339</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>340</v>
-      </c>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
+      <c r="A61" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="B61" s="35"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
     </row>
     <row r="62" ht="18" spans="1:7">
       <c r="A62" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B62" s="34"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16" t="s">
-        <v>342</v>
+        <v>346</v>
+      </c>
+      <c r="B62" s="35"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17" t="s">
+        <v>347</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
+        <v>348</v>
+      </c>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
     </row>
     <row r="63" ht="18" hidden="1" spans="1:7">
-      <c r="A63" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B63" s="34"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16" t="s">
-        <v>345</v>
-      </c>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
+      <c r="A63" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="B63" s="35"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
     </row>
     <row r="64" ht="36" spans="1:7">
-      <c r="A64" s="35" t="s">
-        <v>346</v>
-      </c>
-      <c r="B64" s="35" t="s">
-        <v>347</v>
-      </c>
-      <c r="C64" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
+      <c r="A64" s="36" t="s">
+        <v>351</v>
+      </c>
+      <c r="B64" s="36" t="s">
+        <v>352</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
     </row>
     <row r="65" ht="18" spans="1:7">
-      <c r="A65" s="16" t="s">
-        <v>349</v>
+      <c r="A65" s="17" t="s">
+        <v>354</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
+        <v>356</v>
+      </c>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
+      <c r="G65" s="17"/>
     </row>
     <row r="66" ht="18" spans="1:7">
-      <c r="A66" s="16" t="s">
-        <v>352</v>
+      <c r="A66" s="17" t="s">
+        <v>357</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
+        <v>358</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
     </row>
     <row r="67" ht="36" spans="1:7">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="B67" s="35" t="s">
+        <v>361</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+    </row>
+    <row r="68" ht="18" spans="1:7">
+      <c r="A68" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="B68" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="C68" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+    </row>
+    <row r="69" ht="18" spans="1:7">
+      <c r="A69" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="17"/>
+    </row>
+    <row r="70" ht="19.8" spans="1:7">
+      <c r="A70" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="17"/>
+    </row>
+    <row r="71" ht="36" spans="1:7">
+      <c r="A71" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+    </row>
+    <row r="72" ht="19.8" spans="1:7">
+      <c r="A72" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C72" s="17"/>
+      <c r="D72" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="E72" s="18"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="17"/>
+    </row>
+    <row r="73" ht="19.8" spans="1:7">
+      <c r="A73" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C73" s="17"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="17"/>
+      <c r="G73" s="17"/>
+    </row>
+    <row r="74" ht="19.8" spans="1:7">
+      <c r="A74" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C74" s="17"/>
+      <c r="D74" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="E74" s="18"/>
+      <c r="F74" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="G74" s="26" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="75" ht="19.8" spans="1:7">
+      <c r="A75" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="D75" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="G75" s="17"/>
+    </row>
+    <row r="76" ht="19.8" spans="1:7">
+      <c r="A76" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" s="17"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="17"/>
+      <c r="G76" s="17"/>
+    </row>
+    <row r="77" ht="19.8" spans="1:7">
+      <c r="A77" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C77" s="17"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17"/>
+    </row>
+    <row r="78" ht="36" spans="1:7">
+      <c r="A78" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="17"/>
+    </row>
+    <row r="79" ht="18" spans="1:7">
+      <c r="A79" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B79" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="B67" s="34" t="s">
-        <v>356</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>357</v>
-      </c>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-    </row>
-    <row r="68" ht="18" spans="1:7">
-      <c r="A68" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="B68" s="32" t="s">
-        <v>359</v>
-      </c>
-      <c r="C68" s="32" t="s">
-        <v>360</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16"/>
-    </row>
-    <row r="69" ht="18" spans="1:7">
-      <c r="A69" s="16" t="s">
-        <v>362</v>
-      </c>
-      <c r="B69" s="16"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-    </row>
-    <row r="70" ht="19.8" spans="1:7">
-      <c r="A70" s="16" t="s">
-        <v>363</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="C70" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
-    </row>
-    <row r="71" ht="36" spans="1:7">
-      <c r="A71" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C71" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="D71" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="E71" s="17" t="s">
-        <v>369</v>
-      </c>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
-    </row>
-    <row r="72" ht="19.8" spans="1:7">
-      <c r="A72" s="16" t="s">
-        <v>370</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C72" s="16"/>
-      <c r="D72" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="E72" s="17"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16"/>
-    </row>
-    <row r="73" ht="19.8" spans="1:7">
-      <c r="A73" s="16" t="s">
-        <v>372</v>
-      </c>
-      <c r="B73" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C73" s="16"/>
-      <c r="D73" s="17"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16"/>
-    </row>
-    <row r="74" ht="19.8" spans="1:7">
-      <c r="A74" s="16" t="s">
-        <v>373</v>
-      </c>
-      <c r="B74" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C74" s="16"/>
-      <c r="D74" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="E74" s="17"/>
-      <c r="F74" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="G74" s="25" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="75" ht="19.8" spans="1:7">
-      <c r="A75" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="B75" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>377</v>
-      </c>
-      <c r="D75" s="34" t="s">
-        <v>378</v>
-      </c>
-      <c r="E75" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="F75" s="16" t="s">
-        <v>380</v>
-      </c>
-      <c r="G75" s="16"/>
-    </row>
-    <row r="76" ht="19.8" spans="1:7">
-      <c r="A76" s="16" t="s">
-        <v>381</v>
-      </c>
-      <c r="B76" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C76" s="16"/>
-      <c r="D76" s="17"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-    </row>
-    <row r="77" ht="19.8" spans="1:7">
-      <c r="A77" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B77" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77" s="16"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-    </row>
-    <row r="78" ht="36" spans="1:7">
-      <c r="A78" s="16" t="s">
-        <v>382</v>
-      </c>
-      <c r="B78" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="C78" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="D78" s="17"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16"/>
-    </row>
-    <row r="79" ht="18" spans="1:7">
-      <c r="A79" s="16" t="s">
-        <v>382</v>
-      </c>
-      <c r="B79" s="16" t="s">
-        <v>350</v>
-      </c>
-      <c r="C79" s="16" t="s">
-        <v>385</v>
-      </c>
-      <c r="D79" s="16" t="s">
-        <v>386</v>
-      </c>
-      <c r="E79" s="25" t="s">
-        <v>387</v>
-      </c>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
+      <c r="C79" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="E79" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="F79" s="17"/>
+      <c r="G79" s="17"/>
     </row>
     <row r="80" ht="19.8" spans="1:7">
-      <c r="A80" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="B80" s="16" t="s">
-        <v>350</v>
-      </c>
-      <c r="C80" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16"/>
+      <c r="A80" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="D80" s="17"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17"/>
+      <c r="G80" s="17"/>
     </row>
     <row r="81" ht="19.8" spans="1:7">
-      <c r="A81" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="B81" s="16" t="s">
-        <v>350</v>
-      </c>
-      <c r="C81" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16"/>
+      <c r="A81" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="C81" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
     </row>
     <row r="82" ht="18" spans="1:7">
-      <c r="A82" s="16" t="s">
-        <v>392</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>393</v>
-      </c>
-      <c r="C82" s="16" t="s">
-        <v>394</v>
-      </c>
-      <c r="D82" s="16"/>
-      <c r="E82" s="16"/>
-      <c r="F82" s="16"/>
-      <c r="G82" s="16"/>
+      <c r="A82" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="B82" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="D82" s="17"/>
+      <c r="E82" s="17"/>
+      <c r="F82" s="17"/>
+      <c r="G82" s="17"/>
     </row>
     <row r="83" ht="36" spans="1:7">
-      <c r="A83" s="32" t="s">
-        <v>395</v>
-      </c>
-      <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="33" t="s">
-        <v>273</v>
-      </c>
-      <c r="E83" s="36" t="s">
-        <v>396</v>
-      </c>
-      <c r="F83" s="16"/>
-      <c r="G83" s="16"/>
+      <c r="A83" s="33" t="s">
+        <v>400</v>
+      </c>
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="34" t="s">
+        <v>278</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="F83" s="17"/>
+      <c r="G83" s="17"/>
     </row>
     <row r="84" ht="18" spans="1:7">
-      <c r="A84" s="32" t="s">
-        <v>397</v>
-      </c>
-      <c r="D84" s="34" t="s">
-        <v>398</v>
-      </c>
-      <c r="E84" s="32" t="s">
-        <v>399</v>
-      </c>
-      <c r="F84" s="16"/>
-      <c r="G84" s="16"/>
+      <c r="A84" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="D84" s="35" t="s">
+        <v>403</v>
+      </c>
+      <c r="E84" s="33" t="s">
+        <v>404</v>
+      </c>
+      <c r="F84" s="17"/>
+      <c r="G84" s="17"/>
     </row>
     <row r="85" ht="18" spans="1:7">
-      <c r="A85" s="32" t="s">
-        <v>400</v>
+      <c r="A85" s="33" t="s">
+        <v>405</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="C85" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="D85" s="24" t="s">
-        <v>403</v>
-      </c>
-      <c r="E85" s="16"/>
-      <c r="F85" s="16"/>
-      <c r="G85" s="16"/>
+        <v>406</v>
+      </c>
+      <c r="C85" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="D85" s="25" t="s">
+        <v>408</v>
+      </c>
+      <c r="E85" s="17"/>
+      <c r="F85" s="17"/>
+      <c r="G85" s="17"/>
     </row>
     <row r="86" ht="18" spans="1:7">
-      <c r="A86" s="16" t="s">
-        <v>404</v>
-      </c>
-      <c r="B86" s="16"/>
-      <c r="D86" s="16" t="s">
-        <v>405</v>
-      </c>
-      <c r="E86" s="37" t="s">
-        <v>406</v>
-      </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="16"/>
+      <c r="A86" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="B86" s="17"/>
+      <c r="D86" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="E86" s="38" t="s">
+        <v>411</v>
+      </c>
+      <c r="F86" s="17"/>
+      <c r="G86" s="17"/>
     </row>
     <row r="87" ht="18" spans="1:7">
-      <c r="A87" s="16" t="s">
-        <v>407</v>
-      </c>
-      <c r="B87" s="16"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="16" t="s">
-        <v>408</v>
+      <c r="A87" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="17" t="s">
+        <v>413</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="F87" s="16"/>
-      <c r="G87" s="16"/>
+        <v>414</v>
+      </c>
+      <c r="F87" s="17"/>
+      <c r="G87" s="17"/>
     </row>
     <row r="88" ht="18" spans="1:7">
-      <c r="A88" s="16" t="s">
-        <v>410</v>
-      </c>
-      <c r="B88" s="16"/>
-      <c r="C88" s="16"/>
-      <c r="D88" s="16" t="s">
-        <v>411</v>
+      <c r="A88" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="B88" s="17"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="17" t="s">
+        <v>416</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="F88" s="16"/>
-      <c r="G88" s="16"/>
+        <v>417</v>
+      </c>
+      <c r="F88" s="17"/>
+      <c r="G88" s="17"/>
     </row>
     <row r="89" ht="18" spans="1:7">
-      <c r="A89" s="16" t="s">
-        <v>413</v>
-      </c>
-      <c r="B89" s="16"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="38" t="s">
-        <v>414</v>
-      </c>
-      <c r="E89" s="16"/>
-      <c r="F89" s="16"/>
-      <c r="G89" s="16"/>
+      <c r="A89" s="17" t="s">
+        <v>418</v>
+      </c>
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="39" t="s">
+        <v>419</v>
+      </c>
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
+      <c r="G89" s="17"/>
     </row>
     <row r="90" ht="36" spans="1:7">
-      <c r="A90" s="16" t="s">
-        <v>415</v>
-      </c>
-      <c r="B90" s="16" t="s">
-        <v>416</v>
-      </c>
-      <c r="C90" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="F90" s="16"/>
-      <c r="G90" s="16"/>
+      <c r="A90" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B90" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="F90" s="17"/>
+      <c r="G90" s="17"/>
     </row>
     <row r="91" ht="18" spans="1:7">
-      <c r="A91" s="16" t="s">
-        <v>418</v>
-      </c>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="16" t="s">
-        <v>419</v>
-      </c>
-      <c r="E91" s="16"/>
+      <c r="A91" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="E91" s="17"/>
       <c r="F91" s="4" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="92" ht="18" spans="1:7">
-      <c r="A92" s="16" t="s">
-        <v>422</v>
-      </c>
-      <c r="B92" s="16"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="16" t="s">
-        <v>419</v>
-      </c>
-      <c r="E92" s="16"/>
-      <c r="F92" s="16"/>
-      <c r="G92" s="16"/>
+      <c r="A92" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="B92" s="17"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="E92" s="17"/>
+      <c r="F92" s="17"/>
+      <c r="G92" s="17"/>
     </row>
     <row r="93" ht="18" spans="1:7">
-      <c r="A93" s="16" t="s">
-        <v>423</v>
-      </c>
-      <c r="B93" s="16"/>
-      <c r="C93" s="16"/>
-      <c r="D93" s="16" t="s">
-        <v>419</v>
-      </c>
-      <c r="E93" s="16" t="s">
+      <c r="A93" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="F93" s="16"/>
-      <c r="G93" s="16"/>
+      <c r="E93" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="F93" s="17"/>
+      <c r="G93" s="17"/>
     </row>
     <row r="94" ht="18" spans="1:7">
-      <c r="A94" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="B94" s="16"/>
-      <c r="C94" s="16"/>
-      <c r="D94" s="39" t="s">
-        <v>426</v>
-      </c>
-      <c r="E94" s="16" t="s">
-        <v>427</v>
-      </c>
-      <c r="F94" s="16"/>
-      <c r="G94" s="16"/>
+      <c r="A94" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="B94" s="17"/>
+      <c r="C94" s="17"/>
+      <c r="D94" s="40" t="s">
+        <v>431</v>
+      </c>
+      <c r="E94" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="F94" s="17"/>
+      <c r="G94" s="17"/>
     </row>
     <row r="95" ht="19.8" spans="1:7">
-      <c r="A95" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="B95" s="40" t="s">
-        <v>429</v>
-      </c>
-      <c r="C95" s="16"/>
-      <c r="D95" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="E95" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="F95" s="16"/>
-      <c r="G95" s="16"/>
+      <c r="A95" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="B95" s="41" t="s">
+        <v>434</v>
+      </c>
+      <c r="C95" s="17"/>
+      <c r="D95" s="17" t="s">
+        <v>435</v>
+      </c>
+      <c r="E95" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="F95" s="17"/>
+      <c r="G95" s="17"/>
     </row>
     <row r="96" ht="36" spans="1:7">
-      <c r="A96" s="16" t="s">
-        <v>432</v>
+      <c r="A96" s="17" t="s">
+        <v>437</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C96" s="18" t="s">
-        <v>433</v>
-      </c>
-      <c r="D96" s="16"/>
-      <c r="E96" s="16"/>
-      <c r="F96" s="16"/>
-      <c r="G96" s="16"/>
+        <v>165</v>
+      </c>
+      <c r="C96" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="D96" s="17"/>
+      <c r="E96" s="17"/>
+      <c r="F96" s="17"/>
+      <c r="G96" s="17"/>
     </row>
     <row r="97" ht="18" spans="1:7">
-      <c r="A97" s="19" t="s">
-        <v>434</v>
-      </c>
-      <c r="B97" s="16"/>
-      <c r="C97" s="16"/>
-      <c r="D97" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="E97" s="16"/>
-      <c r="F97" s="16"/>
-      <c r="G97" s="16"/>
+      <c r="A97" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="B97" s="17"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="E97" s="17"/>
+      <c r="F97" s="17"/>
+      <c r="G97" s="17"/>
     </row>
     <row r="98" ht="18" spans="1:7">
-      <c r="A98" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="B98" s="16" t="s">
-        <v>437</v>
-      </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="E98" s="16" t="s">
-        <v>439</v>
-      </c>
-      <c r="F98" s="16" t="s">
-        <v>440</v>
-      </c>
-      <c r="G98" s="16"/>
+      <c r="A98" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="B98" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="C98" s="17"/>
+      <c r="D98" s="35" t="s">
+        <v>443</v>
+      </c>
+      <c r="E98" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="F98" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="G98" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6939,7 +7009,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
@@ -6950,322 +7020,331 @@
   <sheetData>
     <row r="1" ht="18" spans="1:13">
       <c r="I1" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="L1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:13">
       <c r="A2" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B3" t="s">
+        <v>458</v>
+      </c>
+      <c r="E3" t="s">
+        <v>459</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="E3" t="s">
-        <v>454</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>448</v>
-      </c>
       <c r="G3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="K3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="G4" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E5" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:13">
       <c r="E6" s="2" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:13">
       <c r="A7" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:13">
       <c r="A8" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="E8" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:13">
       <c r="A9" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C10" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C11" t="s">
-        <v>508</v>
+        <v>513</v>
+      </c>
+      <c r="E11" t="s">
+        <v>514</v>
+      </c>
+      <c r="F11" t="s">
+        <v>515</v>
+      </c>
+      <c r="G11" t="s">
+        <v>516</v>
       </c>
       <c r="I11" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C14" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="K14" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>527</v>
+        <v>534</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>535</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" ht="18" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C16" s="12"/>
+        <v>537</v>
+      </c>
+      <c r="C16" s="13"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
     <row r="17" ht="18" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C17" s="12"/>
+        <v>539</v>
+      </c>
+      <c r="C17" s="13"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
@@ -7275,68 +7354,79 @@
     </row>
     <row r="19" ht="18" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:10">
       <c r="A20" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>549</v>
+        <v>556</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>558</v>
+      </c>
+      <c r="B25" t="s">
+        <v>559</v>
+      </c>
+      <c r="C25" t="s">
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -7348,7 +7438,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:T35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="13.8888888888889" customWidth="1"/>
@@ -7361,689 +7451,697 @@
   <sheetData>
     <row r="1" ht="18" spans="1:20">
       <c r="A1" s="2" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:20">
       <c r="A2" s="8" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="G2" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="I2" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="O2" t="s">
+        <v>573</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="O2" t="s">
+      <c r="T2" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:20">
       <c r="A3" s="8" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="G3" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:20">
       <c r="A4" s="2" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="G4" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="K4" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="L4" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="M4" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="O4" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="P4" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:20">
       <c r="A5" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:20">
       <c r="A6" s="8" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="G6" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:20">
       <c r="A7" s="8" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="Q7" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:20">
       <c r="A8" s="8" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="G8" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="K8" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="L8" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:20">
       <c r="A9" s="8" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="G9" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:20">
       <c r="A10" s="2" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
       <c r="B10" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>640</v>
+        <v>651</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="I10" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:20">
       <c r="A11" s="2" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="I11" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="Q11" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:20">
       <c r="A12" s="8" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>661</v>
+        <v>672</v>
       </c>
       <c r="I12" t="s">
-        <v>662</v>
+        <v>673</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:20">
       <c r="A13" s="2" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="Q13" t="s">
-        <v>670</v>
+        <v>681</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:20">
       <c r="A14" s="2" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="Q14" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:20">
       <c r="A15" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:20">
       <c r="A16" s="10" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="O16" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
-      <c r="A17" s="10" t="s">
-        <v>690</v>
+      <c r="A17" s="11" t="s">
+        <v>695</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" s="10" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
-      <c r="A19" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>704</v>
+      <c r="A19" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>714</v>
       </c>
       <c r="G19" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="H19" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="A20" s="2" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="C20" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="G20" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="H20" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="O20" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="P20" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
       <c r="A21" s="2" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="O21" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="P21" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
-      <c r="A25" t="s">
-        <v>726</v>
+      <c r="A25" s="2" t="s">
+        <v>736</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
-      <c r="A26" s="2" t="s">
-        <v>728</v>
+      <c r="A26" t="s">
+        <v>738</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>729</v>
+        <v>739</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
-      <c r="A27" s="11" t="s">
-        <v>730</v>
+      <c r="A27" s="2" t="s">
+        <v>740</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
-      <c r="A28" s="2" t="s">
-        <v>732</v>
+      <c r="A28" s="12" t="s">
+        <v>742</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="C28" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
       <c r="E28" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="A29" s="2" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="C29" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
-      <c r="A30" t="s">
-        <v>738</v>
+      <c r="A30" s="2" t="s">
+        <v>749</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
-      <c r="A31" s="2" t="s">
-        <v>740</v>
+      <c r="A31" t="s">
+        <v>750</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>741</v>
+        <v>751</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>743</v>
+        <v>753</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:2">
       <c r="A33" s="2" t="s">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>745</v>
+        <v>755</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>746</v>
+        <v>756</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>747</v>
+        <v>757</v>
+      </c>
+    </row>
+    <row r="35" ht="18" spans="1:2">
+      <c r="A35" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>759</v>
       </c>
     </row>
   </sheetData>
@@ -8055,7 +8153,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G24"/>
+  <dimension ref="A2:G25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -8065,318 +8163,329 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="D4" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="B5" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="D5" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>94</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="D6" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="C10" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="C11" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="C12" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="D12" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="E12" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="C15" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="D15" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="E15" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="F15" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="D16" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="E16" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="F16" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
     </row>
     <row r="17" ht="15.6" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
     </row>
     <row r="18" ht="15.6" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="B22" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="C22" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="B23" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="B24" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="C24" t="s">
-        <v>836</v>
+        <v>848</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>849</v>
+      </c>
+      <c r="B25" t="s">
+        <v>850</v>
+      </c>
+      <c r="C25" t="s">
+        <v>851</v>
       </c>
     </row>
   </sheetData>
@@ -8399,315 +8508,321 @@
   <sheetData>
     <row r="2" ht="18" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>839</v>
+        <v>854</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
       <c r="K2" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="L2" t="s">
-        <v>843</v>
+        <v>858</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>844</v>
+        <v>859</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="K3" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>851</v>
+        <v>866</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>852</v>
+        <v>867</v>
       </c>
       <c r="C4" t="s">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>854</v>
+        <v>869</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="H4" t="s">
-        <v>856</v>
+        <v>871</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>857</v>
+        <v>872</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>859</v>
+        <v>874</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>860</v>
+        <v>875</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>861</v>
+        <v>876</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>863</v>
+        <v>878</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" ht="18" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>869</v>
+        <v>884</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>870</v>
+        <v>885</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>871</v>
+        <v>886</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>872</v>
+        <v>887</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>875</v>
+        <v>890</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>876</v>
+        <v>891</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>877</v>
+        <v>892</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>881</v>
+        <v>896</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>883</v>
+        <v>898</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>884</v>
+        <v>899</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>888</v>
+        <v>903</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>889</v>
+        <v>904</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>891</v>
+        <v>906</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>893</v>
+        <v>908</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>893</v>
+        <v>908</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>894</v>
+        <v>909</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>895</v>
+        <v>910</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>897</v>
+        <v>912</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>902</v>
+        <v>917</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>904</v>
+        <v>919</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>906</v>
+        <v>921</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>907</v>
+        <v>922</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>908</v>
+        <v>923</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>909</v>
+        <v>924</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>910</v>
+        <v>925</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>912</v>
+        <v>927</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>913</v>
+        <v>928</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>914</v>
+        <v>929</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>915</v>
+        <v>930</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>916</v>
+        <v>931</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>918</v>
+        <v>933</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>919</v>
+        <v>934</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" t="s">
-        <v>920</v>
+        <v>935</v>
       </c>
       <c r="G18" t="s">
-        <v>921</v>
+        <v>936</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>923</v>
+        <v>938</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
     <row r="20" ht="18" spans="1:7">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="A20" t="s">
+        <v>921</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>939</v>
+      </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
@@ -8720,7 +8835,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9.55555555555556" style="2" customWidth="1"/>
@@ -8738,237 +8853,245 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>924</v>
+        <v>940</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>925</v>
+        <v>941</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>926</v>
+        <v>942</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>927</v>
+        <v>943</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>928</v>
+        <v>944</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>929</v>
+        <v>945</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>914</v>
+        <v>929</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>915</v>
+        <v>930</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>930</v>
+        <v>946</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>931</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>932</v>
+        <v>948</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>933</v>
+        <v>949</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>934</v>
+        <v>950</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>935</v>
+        <v>951</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>936</v>
+        <v>952</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>937</v>
+        <v>953</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>938</v>
+        <v>954</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>939</v>
+        <v>955</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>940</v>
+        <v>956</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>941</v>
+        <v>957</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>942</v>
+        <v>958</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>943</v>
+        <v>959</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>944</v>
+        <v>960</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>945</v>
+        <v>961</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>946</v>
+        <v>962</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>947</v>
+        <v>963</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>949</v>
+        <v>965</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>950</v>
+        <v>966</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>951</v>
+        <v>967</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>952</v>
+        <v>968</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>953</v>
+        <v>969</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>954</v>
+        <v>970</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>955</v>
+        <v>971</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>956</v>
+        <v>972</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>957</v>
+        <v>973</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>958</v>
+        <v>974</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>959</v>
+        <v>975</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>960</v>
+        <v>976</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>961</v>
+        <v>977</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>962</v>
+        <v>978</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>963</v>
+        <v>979</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>964</v>
+        <v>980</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>965</v>
+        <v>981</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>966</v>
+        <v>982</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>967</v>
+        <v>983</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>969</v>
+        <v>985</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>908</v>
+        <v>923</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>909</v>
+        <v>924</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>971</v>
+        <v>987</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>972</v>
+        <v>988</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>973</v>
+        <v>989</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>974</v>
+        <v>990</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>975</v>
+        <v>991</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>976</v>
+        <v>992</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>977</v>
+        <v>993</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>978</v>
+        <v>994</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>995</v>
+      </c>
+      <c r="B31" t="s">
+        <v>996</v>
       </c>
     </row>
   </sheetData>
@@ -8988,10 +9111,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>979</v>
+        <v>997</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>980</v>
+        <v>998</v>
       </c>
     </row>
   </sheetData>

--- a/Words(音读音 & 训练音).xlsx
+++ b/Words(音读音 & 训练音).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Object(もの)" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="1009">
   <si>
     <t>名称</t>
   </si>
@@ -645,6 +645,15 @@
     <t>しょうそく</t>
   </si>
   <si>
+    <t>混合</t>
+  </si>
+  <si>
+    <t>こんごう</t>
+  </si>
+  <si>
+    <t>（混合）</t>
+  </si>
+  <si>
     <t>効用</t>
   </si>
   <si>
@@ -775,6 +784,12 @@
     <t>しつりょ</t>
   </si>
   <si>
+    <t>結論</t>
+  </si>
+  <si>
+    <t>けつろん</t>
+  </si>
+  <si>
     <t>標準</t>
   </si>
   <si>
@@ -2742,6 +2757,12 @@
   </si>
   <si>
     <t>うなぎ</t>
+  </si>
+  <si>
+    <t>賞味期限</t>
+  </si>
+  <si>
+    <t>しょうみきげん</t>
   </si>
   <si>
     <t>鰻丼</t>
@@ -3182,6 +3203,15 @@
   </si>
   <si>
     <t>つうちょう</t>
+  </si>
+  <si>
+    <t>水道水</t>
+  </si>
+  <si>
+    <t>すいどうすい</t>
+  </si>
+  <si>
+    <t>（自来水）</t>
   </si>
   <si>
     <t>銀行通帳</t>
@@ -5389,70 +5419,79 @@
       <c r="F21" s="2" t="s">
         <v>128</v>
       </c>
+      <c r="I21" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -5463,46 +5502,52 @@
         <v>103</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -5530,28 +5575,28 @@
     <row r="1" s="14" customFormat="1" ht="18" spans="1:7">
       <c r="A1" s="16"/>
       <c r="B1" s="16" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G1" s="16"/>
     </row>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="17" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
@@ -5559,48 +5604,48 @@
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="17" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F3" s="17"/>
       <c r="G3" s="17"/>
     </row>
     <row r="4" ht="19.8" spans="1:7">
       <c r="A4" s="18" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
     </row>
     <row r="5" ht="36" spans="1:7">
       <c r="A5" s="17" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="17"/>
@@ -5608,32 +5653,32 @@
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="17" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
     </row>
     <row r="7" ht="36" spans="1:7">
       <c r="A7" s="17" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -5642,13 +5687,13 @@
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="17" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
@@ -5657,32 +5702,32 @@
     </row>
     <row r="9" ht="19.8" spans="1:7">
       <c r="A9" s="18" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="18" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" ht="19.8" spans="1:7">
       <c r="A10" s="18" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="17"/>
@@ -5691,25 +5736,25 @@
     </row>
     <row r="11" ht="19.8" spans="1:7">
       <c r="A11" s="18" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B11" s="20"/>
       <c r="D11" s="22" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F11" s="24"/>
       <c r="G11" s="17"/>
     </row>
     <row r="12" ht="19.8" spans="1:7">
       <c r="A12" s="18" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B12" s="20"/>
       <c r="D12" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="18"/>
@@ -5717,47 +5762,47 @@
     </row>
     <row r="13" ht="19.8" spans="1:7">
       <c r="A13" s="18" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C13" s="21"/>
       <c r="D13" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F13" s="18"/>
       <c r="G13" s="17"/>
     </row>
     <row r="14" ht="19.8" spans="1:7">
       <c r="A14" s="18" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="21"/>
       <c r="D14" s="25" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F14" s="18"/>
       <c r="G14" s="17"/>
     </row>
     <row r="15" ht="19.8" spans="1:7">
       <c r="A15" s="18" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="21"/>
       <c r="D15" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F15" s="18"/>
       <c r="G15" s="17"/>
@@ -5773,132 +5818,132 @@
     </row>
     <row r="17" ht="19.8" spans="1:7">
       <c r="A17" s="18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="17"/>
     </row>
     <row r="18" ht="43.2" spans="1:7">
       <c r="A18" s="18" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="21"/>
       <c r="D18" s="25" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F18" s="18"/>
       <c r="G18" s="17"/>
     </row>
     <row r="19" ht="19.8" spans="1:7">
       <c r="A19" s="18" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F19" s="18"/>
       <c r="G19" s="17"/>
     </row>
     <row r="20" ht="19.8" spans="1:7">
       <c r="A20" s="18" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F20" s="18"/>
       <c r="G20" s="17"/>
     </row>
     <row r="21" ht="19.8" spans="1:7">
       <c r="A21" s="18" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F21" s="18"/>
       <c r="G21" s="17"/>
     </row>
     <row r="22" ht="24" spans="1:7">
       <c r="A22" s="17" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G22" s="29" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:7">
       <c r="A23" s="17" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
     </row>
     <row r="24" ht="18" spans="1:7">
       <c r="A24" s="17" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F24" s="17"/>
       <c r="G24" s="17"/>
     </row>
     <row r="25" ht="18" spans="1:7">
       <c r="A25" s="17" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
@@ -5906,32 +5951,32 @@
     </row>
     <row r="26" ht="72" spans="1:7">
       <c r="A26" s="17" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
     </row>
     <row r="27" ht="18" spans="1:7">
       <c r="A27" s="17" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
@@ -5940,13 +5985,13 @@
     </row>
     <row r="28" ht="18" spans="1:7">
       <c r="A28" s="17" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
@@ -5955,26 +6000,26 @@
     </row>
     <row r="29" ht="18" spans="1:7">
       <c r="A29" s="17" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="26" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G29" s="17"/>
     </row>
     <row r="30" ht="18" spans="1:7">
       <c r="A30" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -5985,76 +6030,76 @@
     </row>
     <row r="31" ht="18" spans="1:7">
       <c r="A31" s="17" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="26" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:7">
       <c r="A32" s="31" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="17"/>
       <c r="D32" s="26" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
     </row>
     <row r="33" ht="18" spans="1:7">
       <c r="A33" s="32" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="26" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F33" s="26"/>
       <c r="G33" s="26"/>
     </row>
     <row r="34" ht="18" spans="1:7">
       <c r="A34" s="17" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B34" s="17"/>
       <c r="D34" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F34" s="17"/>
       <c r="G34" s="17"/>
     </row>
     <row r="35" ht="18" spans="1:7">
       <c r="A35" s="17" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="17" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
@@ -6062,7 +6107,7 @@
     </row>
     <row r="36" ht="18" spans="1:7">
       <c r="A36" s="17" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -6073,12 +6118,12 @@
     </row>
     <row r="37" ht="18" spans="1:7">
       <c r="A37" s="33" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="34" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="17"/>
@@ -6086,45 +6131,45 @@
     </row>
     <row r="38" ht="18" spans="1:7">
       <c r="A38" s="17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
       <c r="D38" s="7" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="4" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G38" s="17"/>
     </row>
     <row r="39" ht="18" spans="1:7">
       <c r="A39" s="17" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
       <c r="D39" s="4" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G39" s="17"/>
     </row>
     <row r="40" ht="18" spans="1:7">
       <c r="A40" s="17" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="17"/>
@@ -6133,10 +6178,10 @@
     </row>
     <row r="41" ht="18" spans="1:7">
       <c r="A41" s="17" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -6146,10 +6191,10 @@
     </row>
     <row r="42" ht="18" spans="1:7">
       <c r="A42" s="17" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C42" s="17"/>
       <c r="D42" s="17"/>
@@ -6159,7 +6204,7 @@
     </row>
     <row r="43" ht="18" spans="1:7">
       <c r="A43" s="17" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B43" s="17"/>
       <c r="D43" s="17"/>
@@ -6169,7 +6214,7 @@
     </row>
     <row r="44" ht="18" spans="1:7">
       <c r="A44" s="17" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B44" s="17"/>
       <c r="D44" s="17"/>
@@ -6179,83 +6224,83 @@
     </row>
     <row r="45" ht="18" spans="1:7">
       <c r="A45" s="17" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F45" s="17"/>
       <c r="G45" s="17"/>
     </row>
     <row r="46" ht="43.2" spans="1:7">
       <c r="A46" s="17" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F46" s="17"/>
       <c r="G46" s="17"/>
     </row>
     <row r="47" ht="28.8" spans="1:7">
       <c r="A47" s="17" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
       <c r="D47" s="4" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:7">
       <c r="A48" s="17" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
       <c r="D48" s="4"/>
       <c r="E48" s="26" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="26"/>
     </row>
     <row r="49" ht="36" spans="1:7">
       <c r="A49" s="17" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="26"/>
@@ -6264,13 +6309,13 @@
     </row>
     <row r="50" ht="36" spans="1:7">
       <c r="A50" s="7" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="17"/>
@@ -6279,7 +6324,7 @@
     </row>
     <row r="51" ht="18" spans="1:7">
       <c r="A51" s="17" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -6290,7 +6335,7 @@
     </row>
     <row r="52" ht="18" spans="1:7">
       <c r="A52" s="17" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -6301,7 +6346,7 @@
     </row>
     <row r="53" ht="18" spans="1:7">
       <c r="A53" s="17" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -6312,24 +6357,24 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="15" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:7">
       <c r="A55" s="17" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="17"/>
@@ -6338,13 +6383,13 @@
     </row>
     <row r="56" ht="18" spans="1:7">
       <c r="A56" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="17"/>
@@ -6353,54 +6398,54 @@
     </row>
     <row r="57" ht="36" spans="1:7">
       <c r="A57" s="17" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:7">
       <c r="A58" s="17" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B58" s="35" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
     </row>
     <row r="59" ht="18" spans="1:7">
       <c r="A59" s="17" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B59" s="35"/>
       <c r="C59" s="17"/>
       <c r="D59" s="17" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E59" s="17"/>
       <c r="F59" s="17"/>
@@ -6408,12 +6453,12 @@
     </row>
     <row r="60" ht="18" spans="1:7">
       <c r="A60" s="17" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B60" s="35"/>
       <c r="C60" s="17"/>
       <c r="D60" s="17" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="E60" s="17"/>
       <c r="F60" s="17"/>
@@ -6421,42 +6466,42 @@
     </row>
     <row r="61" ht="18" spans="1:7">
       <c r="A61" s="17" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B61" s="35"/>
       <c r="C61" s="17"/>
       <c r="D61" s="17" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F61" s="17"/>
       <c r="G61" s="17"/>
     </row>
     <row r="62" ht="18" spans="1:7">
       <c r="A62" s="7" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B62" s="35"/>
       <c r="C62" s="17"/>
       <c r="D62" s="17" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F62" s="17"/>
       <c r="G62" s="17"/>
     </row>
     <row r="63" ht="18" hidden="1" spans="1:7">
       <c r="A63" s="17" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B63" s="35"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E63" s="17"/>
       <c r="F63" s="17"/>
@@ -6464,13 +6509,13 @@
     </row>
     <row r="64" ht="36" spans="1:7">
       <c r="A64" s="36" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D64" s="17"/>
       <c r="E64" s="17"/>
@@ -6479,13 +6524,13 @@
     </row>
     <row r="65" ht="18" spans="1:7">
       <c r="A65" s="17" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D65" s="17"/>
       <c r="E65" s="17"/>
@@ -6494,13 +6539,13 @@
     </row>
     <row r="66" ht="18" spans="1:7">
       <c r="A66" s="17" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D66" s="17"/>
       <c r="E66" s="17"/>
@@ -6509,13 +6554,13 @@
     </row>
     <row r="67" ht="36" spans="1:7">
       <c r="A67" s="17" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B67" s="35" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D67" s="17"/>
       <c r="E67" s="17"/>
@@ -6524,16 +6569,16 @@
     </row>
     <row r="68" ht="18" spans="1:7">
       <c r="A68" s="17" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C68" s="33" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
@@ -6541,12 +6586,12 @@
     </row>
     <row r="69" ht="18" spans="1:7">
       <c r="A69" s="17" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
       <c r="D69" s="17" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
@@ -6554,16 +6599,16 @@
     </row>
     <row r="70" ht="19.8" spans="1:7">
       <c r="A70" s="17" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E70" s="17"/>
       <c r="F70" s="17"/>
@@ -6571,33 +6616,33 @@
     </row>
     <row r="71" ht="36" spans="1:7">
       <c r="A71" s="17" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B71" s="18" t="s">
         <v>96</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F71" s="17"/>
       <c r="G71" s="17"/>
     </row>
     <row r="72" ht="19.8" spans="1:7">
       <c r="A72" s="17" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B72" s="18" t="s">
         <v>96</v>
       </c>
       <c r="C72" s="17"/>
       <c r="D72" s="18" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E72" s="18"/>
       <c r="F72" s="17"/>
@@ -6605,7 +6650,7 @@
     </row>
     <row r="73" ht="19.8" spans="1:7">
       <c r="A73" s="17" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B73" s="18" t="s">
         <v>96</v>
@@ -6618,47 +6663,47 @@
     </row>
     <row r="74" ht="19.8" spans="1:7">
       <c r="A74" s="17" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B74" s="18" t="s">
         <v>96</v>
       </c>
       <c r="C74" s="17"/>
       <c r="D74" s="35" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E74" s="18"/>
       <c r="F74" s="25" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="G74" s="26" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="75" ht="19.8" spans="1:7">
       <c r="A75" s="17" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B75" s="18" t="s">
         <v>96</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D75" s="35" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="G75" s="17"/>
     </row>
     <row r="76" ht="19.8" spans="1:7">
       <c r="A76" s="17" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B76" s="18" t="s">
         <v>96</v>
@@ -6684,13 +6729,13 @@
     </row>
     <row r="78" ht="36" spans="1:7">
       <c r="A78" s="17" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D78" s="18"/>
       <c r="E78" s="18"/>
@@ -6699,32 +6744,32 @@
     </row>
     <row r="79" ht="18" spans="1:7">
       <c r="A79" s="17" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F79" s="17"/>
       <c r="G79" s="17"/>
     </row>
     <row r="80" ht="19.8" spans="1:7">
       <c r="A80" s="18" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D80" s="17"/>
       <c r="E80" s="17"/>
@@ -6733,13 +6778,13 @@
     </row>
     <row r="81" ht="19.8" spans="1:7">
       <c r="A81" s="18" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D81" s="17"/>
       <c r="E81" s="17"/>
@@ -6748,13 +6793,13 @@
     </row>
     <row r="82" ht="18" spans="1:7">
       <c r="A82" s="17" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D82" s="17"/>
       <c r="E82" s="17"/>
@@ -6763,44 +6808,44 @@
     </row>
     <row r="83" ht="36" spans="1:7">
       <c r="A83" s="33" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
       <c r="D83" s="34" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E83" s="37" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
     </row>
     <row r="84" ht="18" spans="1:7">
       <c r="A84" s="33" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D84" s="35" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F84" s="17"/>
       <c r="G84" s="17"/>
     </row>
     <row r="85" ht="18" spans="1:7">
       <c r="A85" s="33" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E85" s="17"/>
       <c r="F85" s="17"/>
@@ -6808,56 +6853,56 @@
     </row>
     <row r="86" ht="18" spans="1:7">
       <c r="A86" s="17" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B86" s="17"/>
       <c r="D86" s="17" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E86" s="38" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F86" s="17"/>
       <c r="G86" s="17"/>
     </row>
     <row r="87" ht="18" spans="1:7">
       <c r="A87" s="17" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B87" s="17"/>
       <c r="C87" s="17"/>
       <c r="D87" s="17" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F87" s="17"/>
       <c r="G87" s="17"/>
     </row>
     <row r="88" ht="18" spans="1:7">
       <c r="A88" s="17" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
       <c r="D88" s="17" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F88" s="17"/>
       <c r="G88" s="17"/>
     </row>
     <row r="89" ht="18" spans="1:7">
       <c r="A89" s="17" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B89" s="17"/>
       <c r="C89" s="17"/>
       <c r="D89" s="39" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E89" s="17"/>
       <c r="F89" s="17"/>
@@ -6865,42 +6910,42 @@
     </row>
     <row r="90" ht="36" spans="1:7">
       <c r="A90" s="17" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F90" s="17"/>
       <c r="G90" s="17"/>
     </row>
     <row r="91" ht="18" spans="1:7">
       <c r="A91" s="17" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B91" s="17"/>
       <c r="C91" s="17"/>
       <c r="D91" s="17" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E91" s="17"/>
       <c r="F91" s="4" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="92" ht="18" spans="1:7">
       <c r="A92" s="17" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
       <c r="D92" s="17" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E92" s="17"/>
       <c r="F92" s="17"/>
@@ -6908,60 +6953,60 @@
     </row>
     <row r="93" ht="18" spans="1:7">
       <c r="A93" s="17" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B93" s="17"/>
       <c r="C93" s="17"/>
       <c r="D93" s="17" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F93" s="17"/>
       <c r="G93" s="17"/>
     </row>
     <row r="94" ht="18" spans="1:7">
       <c r="A94" s="17" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
       <c r="D94" s="40" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="F94" s="17"/>
       <c r="G94" s="17"/>
     </row>
     <row r="95" ht="19.8" spans="1:7">
       <c r="A95" s="17" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B95" s="41" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C95" s="17"/>
       <c r="D95" s="17" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F95" s="17"/>
       <c r="G95" s="17"/>
     </row>
     <row r="96" ht="36" spans="1:7">
       <c r="A96" s="17" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D96" s="17"/>
       <c r="E96" s="17"/>
@@ -6970,12 +7015,12 @@
     </row>
     <row r="97" ht="18" spans="1:7">
       <c r="A97" s="20" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B97" s="17"/>
       <c r="C97" s="17"/>
       <c r="D97" s="20" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E97" s="17"/>
       <c r="F97" s="17"/>
@@ -6983,20 +7028,20 @@
     </row>
     <row r="98" ht="18" spans="1:7">
       <c r="A98" s="17" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C98" s="17"/>
       <c r="D98" s="35" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F98" s="17" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="G98" s="17"/>
     </row>
@@ -7020,318 +7065,318 @@
   <sheetData>
     <row r="1" ht="18" spans="1:13">
       <c r="I1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="L1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:13">
       <c r="A2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B3" t="s">
+        <v>463</v>
+      </c>
+      <c r="E3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="E3" t="s">
-        <v>459</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>453</v>
-      </c>
       <c r="G3" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K3" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="G4" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E5" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:13">
       <c r="E6" s="2" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:13">
       <c r="A7" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:13">
       <c r="A8" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E8" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:13">
       <c r="A9" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C10" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C11" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="E11" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F11" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="G11" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="I11" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C14" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="K14" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" ht="18" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C16" s="13"/>
       <c r="I16" s="2"/>
@@ -7339,10 +7384,10 @@
     </row>
     <row r="17" ht="18" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C17" s="13"/>
       <c r="I17" s="2"/>
@@ -7354,79 +7399,79 @@
     </row>
     <row r="19" ht="18" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:10">
       <c r="A20" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B25" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C25" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
   </sheetData>
@@ -7451,697 +7496,703 @@
   <sheetData>
     <row r="1" ht="18" spans="1:20">
       <c r="A1" s="2" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:20">
       <c r="A2" s="8" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="G2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="I2" t="s">
+        <v>575</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="O2" t="s">
+        <v>578</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="T2" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="G2" t="s">
-        <v>568</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="I2" t="s">
-        <v>570</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="O2" t="s">
-        <v>573</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:20">
       <c r="A3" s="8" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="G3" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:20">
       <c r="A4" s="2" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G4" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="K4" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="L4" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="M4" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="O4" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="P4" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:20">
       <c r="A5" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:20">
       <c r="A6" s="8" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="G6" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:20">
       <c r="A7" s="8" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="Q7" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:20">
       <c r="A8" s="8" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="G8" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="K8" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="L8" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:20">
       <c r="A9" s="8" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="G9" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:20">
       <c r="A10" s="2" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B10" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="I10" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:20">
       <c r="A11" s="2" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="I11" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="Q11" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:20">
       <c r="A12" s="8" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="I12" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:20">
       <c r="A13" s="2" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="Q13" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:20">
       <c r="A14" s="2" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="Q14" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:20">
       <c r="A15" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:20">
       <c r="A16" s="10" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="O16" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="A17" s="11" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" s="10" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="A19" s="10" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="G19" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="H19" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="A20" s="2" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="C20" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="G20" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="H20" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="O20" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="P20" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
       <c r="A21" s="2" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="O21" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="P21" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>731</v>
+        <v>736</v>
+      </c>
+      <c r="O22" t="s">
+        <v>737</v>
+      </c>
+      <c r="P22" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="A26" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="A28" s="12" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="C28" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="E28" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="A29" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="C29" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="A30" s="2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
       <c r="A31" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:2">
       <c r="A33" s="2" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:2">
       <c r="A35" s="2" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -8163,329 +8214,338 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="D4" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B5" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="D5" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>94</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="D6" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="C10" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="C11" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="C12" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="D12" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="E12" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="C15" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="D15" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="E15" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="F15" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="D16" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="E16" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="F16" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="17" ht="15.6" spans="1:3">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="17" ht="15.6" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="18" ht="15.6" spans="1:3">
+        <v>838</v>
+      </c>
+      <c r="D17" t="s">
+        <v>839</v>
+      </c>
+      <c r="E17" t="s">
+        <v>840</v>
+      </c>
+      <c r="F17" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="18" ht="15.6" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>832</v>
+        <v>842</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="19" ht="18" spans="1:3">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="19" ht="18" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>834</v>
+        <v>844</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="20" ht="18" spans="1:3">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="20" ht="18" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>836</v>
+        <v>846</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="21" ht="18" spans="1:3">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="21" ht="18" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>838</v>
+        <v>848</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>839</v>
+        <v>849</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>841</v>
+        <v>851</v>
       </c>
       <c r="B22" t="s">
-        <v>842</v>
+        <v>852</v>
       </c>
       <c r="C22" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="B23" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="B24" t="s">
-        <v>847</v>
+        <v>857</v>
       </c>
       <c r="C24" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="B25" t="s">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="C25" t="s">
-        <v>851</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -8508,306 +8568,306 @@
   <sheetData>
     <row r="2" ht="18" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>854</v>
+        <v>864</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="K2" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="L2" t="s">
-        <v>858</v>
+        <v>868</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>863</v>
+        <v>873</v>
       </c>
       <c r="K3" t="s">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>865</v>
+        <v>875</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="C4" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="H4" t="s">
-        <v>871</v>
+        <v>881</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>872</v>
+        <v>882</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>873</v>
+        <v>883</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>874</v>
+        <v>884</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>875</v>
+        <v>885</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>876</v>
+        <v>886</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>877</v>
+        <v>887</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>880</v>
+        <v>890</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>881</v>
+        <v>891</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>882</v>
+        <v>892</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" ht="18" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>883</v>
+        <v>893</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>884</v>
+        <v>894</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>885</v>
+        <v>895</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>886</v>
+        <v>896</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>887</v>
+        <v>897</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>888</v>
+        <v>898</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>889</v>
+        <v>899</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>891</v>
+        <v>901</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>892</v>
+        <v>902</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>893</v>
+        <v>903</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>894</v>
+        <v>904</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>896</v>
+        <v>906</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>897</v>
+        <v>907</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>900</v>
+        <v>910</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>904</v>
+        <v>914</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>905</v>
+        <v>915</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>906</v>
+        <v>916</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>907</v>
+        <v>917</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>908</v>
+        <v>918</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>908</v>
+        <v>918</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>909</v>
+        <v>919</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>910</v>
+        <v>920</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>911</v>
+        <v>921</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>912</v>
+        <v>922</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>913</v>
+        <v>923</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>915</v>
+        <v>925</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>916</v>
+        <v>926</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>917</v>
+        <v>927</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>920</v>
+        <v>930</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>924</v>
+        <v>934</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>926</v>
+        <v>936</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>927</v>
+        <v>937</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>928</v>
+        <v>938</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>929</v>
+        <v>939</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>932</v>
+        <v>942</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>933</v>
+        <v>943</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>934</v>
+        <v>944</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" t="s">
-        <v>935</v>
+        <v>945</v>
       </c>
       <c r="G18" t="s">
-        <v>936</v>
+        <v>946</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>937</v>
+        <v>947</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>938</v>
+        <v>948</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -8815,13 +8875,13 @@
     </row>
     <row r="20" ht="18" spans="1:7">
       <c r="A20" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>939</v>
+        <v>949</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -8853,245 +8913,245 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>941</v>
+        <v>951</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>942</v>
+        <v>952</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>943</v>
+        <v>953</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>945</v>
+        <v>955</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>929</v>
+        <v>939</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>946</v>
+        <v>956</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>947</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>948</v>
+        <v>958</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>949</v>
+        <v>959</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>952</v>
+        <v>962</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>953</v>
+        <v>963</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>954</v>
+        <v>964</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>955</v>
+        <v>965</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>956</v>
+        <v>966</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>957</v>
+        <v>967</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>960</v>
+        <v>970</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>962</v>
+        <v>972</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>963</v>
+        <v>973</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>973</v>
+        <v>983</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>974</v>
+        <v>984</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>981</v>
+        <v>991</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>982</v>
+        <v>992</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>983</v>
+        <v>993</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>924</v>
+        <v>934</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>987</v>
+        <v>997</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>989</v>
+        <v>999</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>992</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>993</v>
+        <v>1003</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B31" t="s">
-        <v>996</v>
+        <v>1006</v>
       </c>
     </row>
   </sheetData>
@@ -9111,10 +9171,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>998</v>
+        <v>1008</v>
       </c>
     </row>
   </sheetData>

--- a/Words(音读音 & 训练音).xlsx
+++ b/Words(音读音 & 训练音).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Object(もの)" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="1011">
   <si>
     <t>名称</t>
   </si>
@@ -3568,6 +3568,12 @@
   </si>
   <si>
     <t>みょうじょうだんたい</t>
+  </si>
+  <si>
+    <t>将棋</t>
+  </si>
+  <si>
+    <t>しょうぎ</t>
   </si>
   <si>
     <t>読書感想｜どくしょかんそう</t>
@@ -8872,6 +8878,12 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
+      <c r="F19" t="s">
+        <v>949</v>
+      </c>
+      <c r="G19" t="s">
+        <v>950</v>
+      </c>
     </row>
     <row r="20" ht="18" spans="1:7">
       <c r="A20" t="s">
@@ -8881,7 +8893,7 @@
         <v>932</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -8913,26 +8925,26 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8945,165 +8957,165 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -9116,42 +9128,42 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B31" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
   </sheetData>
@@ -9171,10 +9183,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
   </sheetData>

--- a/Words(音读音 & 训练音).xlsx
+++ b/Words(音读音 & 训练音).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="5"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Object(もの)" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="愛好（あいこう）" sheetId="12" r:id="rId6"/>
     <sheet name="芸術（げいじゅつ）" sheetId="14" r:id="rId7"/>
     <sheet name="url" sheetId="2" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="15" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="1022">
   <si>
     <t>名称</t>
   </si>
@@ -672,6 +673,15 @@
     <t>新しい境地を切り開く</t>
   </si>
   <si>
+    <t>響き</t>
+  </si>
+  <si>
+    <t>ひびき</t>
+  </si>
+  <si>
+    <t>（回声，回音）</t>
+  </si>
+  <si>
     <t>使い道</t>
   </si>
   <si>
@@ -2745,6 +2755,9 @@
   </si>
   <si>
     <t>さつまいも</t>
+  </si>
+  <si>
+    <t>yuno</t>
   </si>
   <si>
     <t>冷たくなる</t>
@@ -3175,6 +3188,18 @@
     <t>（烟灰缸）</t>
   </si>
   <si>
+    <t>必需品</t>
+  </si>
+  <si>
+    <t>ひつじゅひん</t>
+  </si>
+  <si>
+    <t>灰皿</t>
+  </si>
+  <si>
+    <t>はいざら</t>
+  </si>
+  <si>
     <t>お決まり</t>
   </si>
   <si>
@@ -3184,10 +3209,10 @@
     <t>（惯例，老习惯）</t>
   </si>
   <si>
-    <t>灰皿</t>
-  </si>
-  <si>
-    <t>はいざら</t>
+    <t>通帳</t>
+  </si>
+  <si>
+    <t>つうちょう</t>
   </si>
   <si>
     <t>墓参り</t>
@@ -3199,10 +3224,10 @@
     <t>（上坟）</t>
   </si>
   <si>
-    <t>通帳</t>
-  </si>
-  <si>
-    <t>つうちょう</t>
+    <t>銀行通帳</t>
+  </si>
+  <si>
+    <t>ぎんこうつうちょう</t>
   </si>
   <si>
     <t>水道水</t>
@@ -3214,16 +3239,16 @@
     <t>（自来水）</t>
   </si>
   <si>
-    <t>銀行通帳</t>
-  </si>
-  <si>
-    <t>ぎんこうつうちょう</t>
-  </si>
-  <si>
     <t>枕</t>
   </si>
   <si>
     <t>まくら</t>
+  </si>
+  <si>
+    <t>おもけ</t>
+  </si>
+  <si>
+    <t>（赠品，附录）</t>
   </si>
   <si>
     <t>炊飯器</t>
@@ -3290,6 +3315,15 @@
   </si>
   <si>
     <t>（洗发水）</t>
+  </si>
+  <si>
+    <t>湯飲み</t>
+  </si>
+  <si>
+    <t>ゆのみ</t>
+  </si>
+  <si>
+    <t>（小碗）</t>
   </si>
   <si>
     <t>芸</t>
@@ -5454,50 +5488,59 @@
       <c r="H22" s="2" t="s">
         <v>137</v>
       </c>
+      <c r="I22" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -5508,52 +5551,52 @@
         <v>103</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -5581,28 +5624,28 @@
     <row r="1" s="14" customFormat="1" ht="18" spans="1:7">
       <c r="A1" s="16"/>
       <c r="B1" s="16" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G1" s="16"/>
     </row>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="17" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
@@ -5610,48 +5653,48 @@
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F3" s="17"/>
       <c r="G3" s="17"/>
     </row>
     <row r="4" ht="19.8" spans="1:7">
       <c r="A4" s="18" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
     </row>
     <row r="5" ht="36" spans="1:7">
       <c r="A5" s="17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="17"/>
@@ -5659,32 +5702,32 @@
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
     </row>
     <row r="7" ht="36" spans="1:7">
       <c r="A7" s="17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -5693,13 +5736,13 @@
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="17" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
@@ -5708,32 +5751,32 @@
     </row>
     <row r="9" ht="19.8" spans="1:7">
       <c r="A9" s="18" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="18" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" ht="19.8" spans="1:7">
       <c r="A10" s="18" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="17"/>
@@ -5742,25 +5785,25 @@
     </row>
     <row r="11" ht="19.8" spans="1:7">
       <c r="A11" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B11" s="20"/>
       <c r="D11" s="22" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F11" s="24"/>
       <c r="G11" s="17"/>
     </row>
     <row r="12" ht="19.8" spans="1:7">
       <c r="A12" s="18" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B12" s="20"/>
       <c r="D12" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="18"/>
@@ -5768,47 +5811,47 @@
     </row>
     <row r="13" ht="19.8" spans="1:7">
       <c r="A13" s="18" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C13" s="21"/>
       <c r="D13" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F13" s="18"/>
       <c r="G13" s="17"/>
     </row>
     <row r="14" ht="19.8" spans="1:7">
       <c r="A14" s="18" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="21"/>
       <c r="D14" s="25" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F14" s="18"/>
       <c r="G14" s="17"/>
     </row>
     <row r="15" ht="19.8" spans="1:7">
       <c r="A15" s="18" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="21"/>
       <c r="D15" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F15" s="18"/>
       <c r="G15" s="17"/>
@@ -5824,132 +5867,132 @@
     </row>
     <row r="17" ht="19.8" spans="1:7">
       <c r="A17" s="18" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="17"/>
     </row>
     <row r="18" ht="43.2" spans="1:7">
       <c r="A18" s="18" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="21"/>
       <c r="D18" s="25" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F18" s="18"/>
       <c r="G18" s="17"/>
     </row>
     <row r="19" ht="19.8" spans="1:7">
       <c r="A19" s="18" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F19" s="18"/>
       <c r="G19" s="17"/>
     </row>
     <row r="20" ht="19.8" spans="1:7">
       <c r="A20" s="18" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F20" s="18"/>
       <c r="G20" s="17"/>
     </row>
     <row r="21" ht="19.8" spans="1:7">
       <c r="A21" s="18" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F21" s="18"/>
       <c r="G21" s="17"/>
     </row>
     <row r="22" ht="24" spans="1:7">
       <c r="A22" s="17" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G22" s="29" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:7">
       <c r="A23" s="17" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
     </row>
     <row r="24" ht="18" spans="1:7">
       <c r="A24" s="17" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F24" s="17"/>
       <c r="G24" s="17"/>
     </row>
     <row r="25" ht="18" spans="1:7">
       <c r="A25" s="17" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
@@ -5957,32 +6000,32 @@
     </row>
     <row r="26" ht="72" spans="1:7">
       <c r="A26" s="17" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
     </row>
     <row r="27" ht="18" spans="1:7">
       <c r="A27" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
@@ -5991,13 +6034,13 @@
     </row>
     <row r="28" ht="18" spans="1:7">
       <c r="A28" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
@@ -6006,26 +6049,26 @@
     </row>
     <row r="29" ht="18" spans="1:7">
       <c r="A29" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="26" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G29" s="17"/>
     </row>
     <row r="30" ht="18" spans="1:7">
       <c r="A30" s="30" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -6036,76 +6079,76 @@
     </row>
     <row r="31" ht="18" spans="1:7">
       <c r="A31" s="17" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="26" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:7">
       <c r="A32" s="31" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="17"/>
       <c r="D32" s="26" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
     </row>
     <row r="33" ht="18" spans="1:7">
       <c r="A33" s="32" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="26" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F33" s="26"/>
       <c r="G33" s="26"/>
     </row>
     <row r="34" ht="18" spans="1:7">
       <c r="A34" s="17" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B34" s="17"/>
       <c r="D34" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F34" s="17"/>
       <c r="G34" s="17"/>
     </row>
     <row r="35" ht="18" spans="1:7">
       <c r="A35" s="17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
@@ -6113,7 +6156,7 @@
     </row>
     <row r="36" ht="18" spans="1:7">
       <c r="A36" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -6124,12 +6167,12 @@
     </row>
     <row r="37" ht="18" spans="1:7">
       <c r="A37" s="33" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="34" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="17"/>
@@ -6137,45 +6180,45 @@
     </row>
     <row r="38" ht="18" spans="1:7">
       <c r="A38" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
       <c r="D38" s="7" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G38" s="17"/>
     </row>
     <row r="39" ht="18" spans="1:7">
       <c r="A39" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
       <c r="D39" s="4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G39" s="17"/>
     </row>
     <row r="40" ht="18" spans="1:7">
       <c r="A40" s="17" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="17"/>
@@ -6184,10 +6227,10 @@
     </row>
     <row r="41" ht="18" spans="1:7">
       <c r="A41" s="17" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -6197,10 +6240,10 @@
     </row>
     <row r="42" ht="18" spans="1:7">
       <c r="A42" s="17" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C42" s="17"/>
       <c r="D42" s="17"/>
@@ -6210,7 +6253,7 @@
     </row>
     <row r="43" ht="18" spans="1:7">
       <c r="A43" s="17" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B43" s="17"/>
       <c r="D43" s="17"/>
@@ -6220,7 +6263,7 @@
     </row>
     <row r="44" ht="18" spans="1:7">
       <c r="A44" s="17" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B44" s="17"/>
       <c r="D44" s="17"/>
@@ -6230,83 +6273,83 @@
     </row>
     <row r="45" ht="18" spans="1:7">
       <c r="A45" s="17" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F45" s="17"/>
       <c r="G45" s="17"/>
     </row>
     <row r="46" ht="43.2" spans="1:7">
       <c r="A46" s="17" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F46" s="17"/>
       <c r="G46" s="17"/>
     </row>
     <row r="47" ht="28.8" spans="1:7">
       <c r="A47" s="17" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
       <c r="D47" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:7">
       <c r="A48" s="17" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
       <c r="D48" s="4"/>
       <c r="E48" s="26" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="26"/>
     </row>
     <row r="49" ht="36" spans="1:7">
       <c r="A49" s="17" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="26"/>
@@ -6315,13 +6358,13 @@
     </row>
     <row r="50" ht="36" spans="1:7">
       <c r="A50" s="7" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="17"/>
@@ -6330,7 +6373,7 @@
     </row>
     <row r="51" ht="18" spans="1:7">
       <c r="A51" s="17" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -6341,7 +6384,7 @@
     </row>
     <row r="52" ht="18" spans="1:7">
       <c r="A52" s="17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -6352,7 +6395,7 @@
     </row>
     <row r="53" ht="18" spans="1:7">
       <c r="A53" s="17" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -6363,24 +6406,24 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:7">
       <c r="A55" s="17" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="17"/>
@@ -6389,13 +6432,13 @@
     </row>
     <row r="56" ht="18" spans="1:7">
       <c r="A56" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="17"/>
@@ -6404,54 +6447,54 @@
     </row>
     <row r="57" ht="36" spans="1:7">
       <c r="A57" s="17" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:7">
       <c r="A58" s="17" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B58" s="35" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
     </row>
     <row r="59" ht="18" spans="1:7">
       <c r="A59" s="17" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B59" s="35"/>
       <c r="C59" s="17"/>
       <c r="D59" s="17" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E59" s="17"/>
       <c r="F59" s="17"/>
@@ -6459,12 +6502,12 @@
     </row>
     <row r="60" ht="18" spans="1:7">
       <c r="A60" s="17" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B60" s="35"/>
       <c r="C60" s="17"/>
       <c r="D60" s="17" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E60" s="17"/>
       <c r="F60" s="17"/>
@@ -6472,42 +6515,42 @@
     </row>
     <row r="61" ht="18" spans="1:7">
       <c r="A61" s="17" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B61" s="35"/>
       <c r="C61" s="17"/>
       <c r="D61" s="17" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F61" s="17"/>
       <c r="G61" s="17"/>
     </row>
     <row r="62" ht="18" spans="1:7">
       <c r="A62" s="7" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B62" s="35"/>
       <c r="C62" s="17"/>
       <c r="D62" s="17" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F62" s="17"/>
       <c r="G62" s="17"/>
     </row>
     <row r="63" ht="18" hidden="1" spans="1:7">
       <c r="A63" s="17" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B63" s="35"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E63" s="17"/>
       <c r="F63" s="17"/>
@@ -6515,13 +6558,13 @@
     </row>
     <row r="64" ht="36" spans="1:7">
       <c r="A64" s="36" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D64" s="17"/>
       <c r="E64" s="17"/>
@@ -6530,13 +6573,13 @@
     </row>
     <row r="65" ht="18" spans="1:7">
       <c r="A65" s="17" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D65" s="17"/>
       <c r="E65" s="17"/>
@@ -6545,13 +6588,13 @@
     </row>
     <row r="66" ht="18" spans="1:7">
       <c r="A66" s="17" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D66" s="17"/>
       <c r="E66" s="17"/>
@@ -6560,13 +6603,13 @@
     </row>
     <row r="67" ht="36" spans="1:7">
       <c r="A67" s="17" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B67" s="35" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D67" s="17"/>
       <c r="E67" s="17"/>
@@ -6575,16 +6618,16 @@
     </row>
     <row r="68" ht="18" spans="1:7">
       <c r="A68" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C68" s="33" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
@@ -6592,12 +6635,12 @@
     </row>
     <row r="69" ht="18" spans="1:7">
       <c r="A69" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
       <c r="D69" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
@@ -6605,16 +6648,16 @@
     </row>
     <row r="70" ht="19.8" spans="1:7">
       <c r="A70" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B70" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="D70" s="17" t="s">
         <v>374</v>
-      </c>
-      <c r="C70" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="D70" s="17" t="s">
-        <v>371</v>
       </c>
       <c r="E70" s="17"/>
       <c r="F70" s="17"/>
@@ -6622,33 +6665,33 @@
     </row>
     <row r="71" ht="36" spans="1:7">
       <c r="A71" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B71" s="18" t="s">
         <v>96</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F71" s="17"/>
       <c r="G71" s="17"/>
     </row>
     <row r="72" ht="19.8" spans="1:7">
       <c r="A72" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B72" s="18" t="s">
         <v>96</v>
       </c>
       <c r="C72" s="17"/>
       <c r="D72" s="18" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E72" s="18"/>
       <c r="F72" s="17"/>
@@ -6656,7 +6699,7 @@
     </row>
     <row r="73" ht="19.8" spans="1:7">
       <c r="A73" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B73" s="18" t="s">
         <v>96</v>
@@ -6669,47 +6712,47 @@
     </row>
     <row r="74" ht="19.8" spans="1:7">
       <c r="A74" s="17" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B74" s="18" t="s">
         <v>96</v>
       </c>
       <c r="C74" s="17"/>
       <c r="D74" s="35" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E74" s="18"/>
       <c r="F74" s="25" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G74" s="26" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="75" ht="19.8" spans="1:7">
       <c r="A75" s="17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B75" s="18" t="s">
         <v>96</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D75" s="35" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G75" s="17"/>
     </row>
     <row r="76" ht="19.8" spans="1:7">
       <c r="A76" s="17" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B76" s="18" t="s">
         <v>96</v>
@@ -6735,13 +6778,13 @@
     </row>
     <row r="78" ht="36" spans="1:7">
       <c r="A78" s="17" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D78" s="18"/>
       <c r="E78" s="18"/>
@@ -6750,32 +6793,32 @@
     </row>
     <row r="79" ht="18" spans="1:7">
       <c r="A79" s="17" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F79" s="17"/>
       <c r="G79" s="17"/>
     </row>
     <row r="80" ht="19.8" spans="1:7">
       <c r="A80" s="18" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D80" s="17"/>
       <c r="E80" s="17"/>
@@ -6784,13 +6827,13 @@
     </row>
     <row r="81" ht="19.8" spans="1:7">
       <c r="A81" s="18" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D81" s="17"/>
       <c r="E81" s="17"/>
@@ -6799,13 +6842,13 @@
     </row>
     <row r="82" ht="18" spans="1:7">
       <c r="A82" s="17" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D82" s="17"/>
       <c r="E82" s="17"/>
@@ -6814,44 +6857,44 @@
     </row>
     <row r="83" ht="36" spans="1:7">
       <c r="A83" s="33" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
       <c r="D83" s="34" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E83" s="37" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
     </row>
     <row r="84" ht="18" spans="1:7">
       <c r="A84" s="33" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D84" s="35" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F84" s="17"/>
       <c r="G84" s="17"/>
     </row>
     <row r="85" ht="18" spans="1:7">
       <c r="A85" s="33" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E85" s="17"/>
       <c r="F85" s="17"/>
@@ -6859,56 +6902,56 @@
     </row>
     <row r="86" ht="18" spans="1:7">
       <c r="A86" s="17" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B86" s="17"/>
       <c r="D86" s="17" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E86" s="38" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F86" s="17"/>
       <c r="G86" s="17"/>
     </row>
     <row r="87" ht="18" spans="1:7">
       <c r="A87" s="17" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B87" s="17"/>
       <c r="C87" s="17"/>
       <c r="D87" s="17" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F87" s="17"/>
       <c r="G87" s="17"/>
     </row>
     <row r="88" ht="18" spans="1:7">
       <c r="A88" s="17" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
       <c r="D88" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F88" s="17"/>
       <c r="G88" s="17"/>
     </row>
     <row r="89" ht="18" spans="1:7">
       <c r="A89" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B89" s="17"/>
       <c r="C89" s="17"/>
       <c r="D89" s="39" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E89" s="17"/>
       <c r="F89" s="17"/>
@@ -6916,42 +6959,42 @@
     </row>
     <row r="90" ht="36" spans="1:7">
       <c r="A90" s="17" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F90" s="17"/>
       <c r="G90" s="17"/>
     </row>
     <row r="91" ht="18" spans="1:7">
       <c r="A91" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B91" s="17"/>
       <c r="C91" s="17"/>
       <c r="D91" s="17" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E91" s="17"/>
       <c r="F91" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="92" ht="18" spans="1:7">
       <c r="A92" s="17" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
       <c r="D92" s="17" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E92" s="17"/>
       <c r="F92" s="17"/>
@@ -6959,60 +7002,60 @@
     </row>
     <row r="93" ht="18" spans="1:7">
       <c r="A93" s="17" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B93" s="17"/>
       <c r="C93" s="17"/>
       <c r="D93" s="17" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F93" s="17"/>
       <c r="G93" s="17"/>
     </row>
     <row r="94" ht="18" spans="1:7">
       <c r="A94" s="17" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
       <c r="D94" s="40" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F94" s="17"/>
       <c r="G94" s="17"/>
     </row>
     <row r="95" ht="19.8" spans="1:7">
       <c r="A95" s="17" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B95" s="41" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C95" s="17"/>
       <c r="D95" s="17" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F95" s="17"/>
       <c r="G95" s="17"/>
     </row>
     <row r="96" ht="36" spans="1:7">
       <c r="A96" s="17" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D96" s="17"/>
       <c r="E96" s="17"/>
@@ -7021,12 +7064,12 @@
     </row>
     <row r="97" ht="18" spans="1:7">
       <c r="A97" s="20" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B97" s="17"/>
       <c r="C97" s="17"/>
       <c r="D97" s="20" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E97" s="17"/>
       <c r="F97" s="17"/>
@@ -7034,20 +7077,20 @@
     </row>
     <row r="98" ht="18" spans="1:7">
       <c r="A98" s="17" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C98" s="17"/>
       <c r="D98" s="35" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F98" s="17" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G98" s="17"/>
     </row>
@@ -7071,318 +7114,318 @@
   <sheetData>
     <row r="1" ht="18" spans="1:13">
       <c r="I1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:13">
       <c r="A2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G4" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E5" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:13">
       <c r="E6" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:13">
       <c r="A7" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:13">
       <c r="A8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E8" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:13">
       <c r="A9" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C10" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C11" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E11" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F11" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="G11" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="I11" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C14" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K14" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" ht="18" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C16" s="13"/>
       <c r="I16" s="2"/>
@@ -7390,10 +7433,10 @@
     </row>
     <row r="17" ht="18" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C17" s="13"/>
       <c r="I17" s="2"/>
@@ -7405,79 +7448,79 @@
     </row>
     <row r="19" ht="18" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:10">
       <c r="A20" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B25" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C25" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -7502,703 +7545,706 @@
   <sheetData>
     <row r="1" ht="18" spans="1:20">
       <c r="A1" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:20">
       <c r="A2" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="G2" t="s">
+        <v>576</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="I2" t="s">
+        <v>578</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="O2" t="s">
+        <v>581</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="T2" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>572</v>
-      </c>
-      <c r="G2" t="s">
-        <v>573</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="I2" t="s">
-        <v>575</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="O2" t="s">
-        <v>578</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:20">
       <c r="A3" s="8" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="G3" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:20">
       <c r="A4" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="G4" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="K4" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="L4" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="M4" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="O4" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="P4" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:20">
       <c r="A5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:20">
       <c r="A6" s="8" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="G6" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:20">
       <c r="A7" s="8" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="Q7" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:20">
       <c r="A8" s="8" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="G8" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K8" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L8" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:20">
       <c r="A9" s="8" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="G9" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:20">
       <c r="A10" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B10" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="I10" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:20">
       <c r="A11" s="2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="I11" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="Q11" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:20">
       <c r="A12" s="8" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="I12" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:20">
       <c r="A13" s="2" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="Q13" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:20">
       <c r="A14" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="Q14" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:20">
       <c r="A15" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:20">
       <c r="A16" s="10" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="O16" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:16">
       <c r="A17" s="11" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:16">
       <c r="A18" s="10" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:16">
       <c r="A19" s="10" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="G19" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="H19" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:16">
       <c r="A20" s="2" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C20" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="G20" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="H20" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="O20" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="P20" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:16">
       <c r="A21" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
+      </c>
+      <c r="G21" t="s">
+        <v>736</v>
       </c>
       <c r="O21" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="P21" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:16">
       <c r="A22" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="O22" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="P22" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:16">
       <c r="A23" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:16">
       <c r="A26" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:16">
       <c r="A28" s="12" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C28" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="E28" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:16">
       <c r="A29" s="2" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C29" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:16">
       <c r="A30" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:16">
       <c r="A31" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:2">
       <c r="A33" s="2" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:2">
       <c r="A35" s="2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -8210,7 +8256,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G25"/>
+  <dimension ref="A2:G26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -8220,338 +8266,361 @@
   <sheetData>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="D4" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B5" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="D5" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>94</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="D6" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C10" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C11" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C12" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D12" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="E12" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C15" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="D15" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="E15" t="s">
-        <v>830</v>
-      </c>
-      <c r="F15" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D16" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="E16" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="F16" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="17" ht="15.6" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D17" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E17" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="F17" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="18" ht="15.6" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>843</v>
+        <v>846</v>
+      </c>
+      <c r="D18" t="s">
+        <v>847</v>
+      </c>
+      <c r="E18" t="s">
+        <v>848</v>
+      </c>
+      <c r="F18" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>845</v>
+        <v>851</v>
+      </c>
+      <c r="E19" t="s">
+        <v>852</v>
+      </c>
+      <c r="F19" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="B22" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="C22" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="B23" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="B24" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="C24" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="B25" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="C25" t="s">
-        <v>861</v>
+        <v>869</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>870</v>
+      </c>
+      <c r="B26" t="s">
+        <v>871</v>
+      </c>
+      <c r="C26" t="s">
+        <v>872</v>
       </c>
     </row>
   </sheetData>
@@ -8574,326 +8643,326 @@
   <sheetData>
     <row r="2" ht="18" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>866</v>
+        <v>877</v>
       </c>
       <c r="K2" t="s">
-        <v>867</v>
+        <v>878</v>
       </c>
       <c r="L2" t="s">
-        <v>868</v>
+        <v>879</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>870</v>
+        <v>881</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>871</v>
+        <v>882</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>873</v>
+        <v>884</v>
       </c>
       <c r="K3" t="s">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>875</v>
+        <v>886</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="C4" t="s">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>880</v>
+        <v>891</v>
       </c>
       <c r="H4" t="s">
-        <v>881</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>882</v>
+        <v>893</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>885</v>
+        <v>896</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>887</v>
+        <v>898</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>889</v>
+        <v>900</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>890</v>
+        <v>901</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>891</v>
+        <v>902</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" ht="18" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>893</v>
+        <v>904</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>897</v>
+        <v>908</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>902</v>
+        <v>913</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>906</v>
+        <v>917</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>910</v>
+        <v>921</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>913</v>
+        <v>924</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>916</v>
+        <v>927</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>919</v>
+        <v>930</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>923</v>
+        <v>934</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>926</v>
+        <v>937</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>927</v>
+        <v>938</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>930</v>
+        <v>941</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>932</v>
+        <v>943</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>933</v>
+        <v>944</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>934</v>
+        <v>945</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>935</v>
+        <v>946</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>936</v>
+        <v>947</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>937</v>
+        <v>948</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>938</v>
+        <v>949</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>939</v>
+        <v>950</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>940</v>
+        <v>951</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>941</v>
+        <v>952</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>942</v>
+        <v>953</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" t="s">
-        <v>945</v>
+        <v>956</v>
       </c>
       <c r="G18" t="s">
-        <v>946</v>
+        <v>957</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>947</v>
+        <v>958</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>948</v>
+        <v>959</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" t="s">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="G19" t="s">
-        <v>950</v>
+        <v>961</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:7">
       <c r="A20" t="s">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>932</v>
+        <v>943</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -8925,245 +8994,245 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>952</v>
+        <v>963</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>954</v>
+        <v>965</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>955</v>
+        <v>966</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>957</v>
+        <v>968</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>939</v>
+        <v>950</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>940</v>
+        <v>951</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>958</v>
+        <v>969</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>959</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>960</v>
+        <v>971</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>961</v>
+        <v>972</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>962</v>
+        <v>973</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>963</v>
+        <v>974</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>964</v>
+        <v>975</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>966</v>
+        <v>977</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>967</v>
+        <v>978</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>969</v>
+        <v>980</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>970</v>
+        <v>981</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>973</v>
+        <v>984</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>974</v>
+        <v>985</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>975</v>
+        <v>986</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>976</v>
+        <v>987</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>980</v>
+        <v>991</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>981</v>
+        <v>992</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>982</v>
+        <v>993</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>983</v>
+        <v>994</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>984</v>
+        <v>995</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>985</v>
+        <v>996</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>986</v>
+        <v>997</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>987</v>
+        <v>998</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>988</v>
+        <v>999</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>989</v>
+        <v>1000</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>990</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>991</v>
+        <v>1002</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>995</v>
+        <v>1006</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>996</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>997</v>
+        <v>1008</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>933</v>
+        <v>944</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>934</v>
+        <v>945</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>1003</v>
+        <v>1014</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1006</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>1007</v>
+        <v>1018</v>
       </c>
       <c r="B31" t="s">
-        <v>1008</v>
+        <v>1019</v>
       </c>
     </row>
   </sheetData>
@@ -9183,10 +9252,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>1009</v>
+        <v>1020</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1010</v>
+        <v>1021</v>
       </c>
     </row>
   </sheetData>
@@ -9196,4 +9265,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>